--- a/data_hei/batch-20261003-2347/results.xlsx
+++ b/data_hei/batch-20261003-2347/results.xlsx
@@ -1160,9 +1160,21 @@
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Charlotte Morantin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ITM Education Office</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cmorantin@itg.be</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>erasmusplusmobility@itg.be</t>
@@ -1171,18 +1183,18 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" s="1" t="inlineStr">
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1197,12 +1209,12 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1246,22 +1258,34 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AD6" s="1" t="inlineStr">
+        <is>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Interested? Contact the ITM Education Office (Charlotte Morantin – cmorantin@itg.be &lt;cmorantin@itg.be&gt;) to discuss the existing possibilities.</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>no contact found</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
+          <t>name, email found on page</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Secretary / administration (last resort). Charlotte Morantin is a contact in the ITM Education Office handling outgoing staff mobility options.</t>
+        </is>
+      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>country;contact_name;email</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1271,7 +1295,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>26 of 27 verified</t>
+          <t>34 of 34 verified</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1283,17 +1307,17 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>The evidence provides a list of specific partners in various contexts, but does not contain a comprehensive master list of all Erasmus+ partner institutions.</t>
+          <t>The evidence lists several partner institutions and networks such as Nova Academy and partner universities, but does not contain a comprehensive, exhaustive list of all individual partner institutions.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>site found via: email domain. mode: gemini.</t>
+          <t>site found via: remembered from an earlier run. mode: gemini.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2814,7 +2838,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>name found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -3715,7 +3739,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>name found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3924,39 +3948,40 @@
     <hyperlink ref="N5" location="'r005 34959494600 LYCEE VINCENT'!A1" display="1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId4"/>
-    <hyperlink ref="I6" location="'Needs Review'!A25" display="yes"/>
+    <hyperlink ref="B6" location="'Contacts'!A3" display="Charlotte Morantin"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink ref="M6" location="'r007 PRINS LEOPOLD INSTITUUT VO'!A1" display="27"/>
-    <hyperlink ref="N6" location="'r007 PRINS LEOPOLD INSTITUUT VO'!A1" display="3"/>
+    <hyperlink ref="M6" location="'r007 PRINS LEOPOLD INSTITUUT VO'!A1" display="34"/>
+    <hyperlink ref="N6" location="'r007 PRINS LEOPOLD INSTITUUT VO'!A1" display="2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId6"/>
-    <hyperlink ref="B13" location="'Contacts'!A3" display="Artur Grzesiak"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD6" r:id="rId7"/>
+    <hyperlink ref="B13" location="'Contacts'!A6" display="Artur Grzesiak"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId8"/>
     <hyperlink ref="M13" location="'r015 Lubelska Akademia WSEI'!A1" display="79"/>
     <hyperlink ref="N13" location="'r015 Lubelska Akademia WSEI'!A1" display="2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD13" r:id="rId8"/>
-    <hyperlink ref="B15" location="'Contacts'!A4" display="Szalánczy Gábor"/>
-    <hyperlink ref="I15" location="'Needs Review'!A109" display="yes"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD13" r:id="rId9"/>
+    <hyperlink ref="B15" location="'Contacts'!A7" display="Szalánczy Gábor"/>
+    <hyperlink ref="I15" location="'Needs Review'!A107" display="yes"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
     <hyperlink ref="M15" location="'r018 Europa 2000'!A1" display="13"/>
     <hyperlink ref="N15" location="'r018 Europa 2000'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD15" r:id="rId10"/>
-    <hyperlink ref="B20" location="'Contacts'!A6" display="Edith Zeier-Draxl"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD15" r:id="rId11"/>
+    <hyperlink ref="B20" location="'Contacts'!A9" display="Edith Zeier-Draxl"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId12"/>
     <hyperlink ref="N20" location="'r023 unit'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD20" r:id="rId13"/>
-    <hyperlink ref="I27" location="'Needs Review'!A125" display="yes"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD20" r:id="rId14"/>
+    <hyperlink ref="I27" location="'Needs Review'!A123" display="yes"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId15"/>
     <hyperlink ref="M27" location="'r031 ESCUELA SUPERIOR DE ARTE D'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId15"/>
-    <hyperlink ref="B28" location="'Contacts'!A7" display="Aïda Diab"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId16"/>
+    <hyperlink ref="B28" location="'Contacts'!A10" display="Aïda Diab"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId17"/>
     <hyperlink ref="M28" location="'r032 GROUPE EAC - ING'!A1" display="17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD28" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId19"/>
     <hyperlink ref="M29" location="'r033 UNIVERSITE GRENOBLE ALPES'!A1" display="2"/>
     <hyperlink ref="N29" location="'r033 UNIVERSITE GRENOBLE ALPES'!A1" display="2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5850,7 +5875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6678,12 +6703,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Institut National de Recherche Biomédicale (INRB)</t>
+          <t>Instituto de Medicina Tropical “Pedro Kourí”</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6729,7 +6754,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Toen de huidige ebola-uitbraak in Bundibugyo in DRC de kop opstak, kwamen onderzoekers van ITG-partner Institut National de Recherche Biomédicale (INRB) onmiddellijk in actie. ITG-professor Koen Vercauteren vertelt over de rol van langetermijninvesteringen in sequencing-technologieën en wetenschappelijke samenwerkingsverbanden.</t>
+          <t>Yanisley Martínez López, Instituto de Medicina Tropical “Pedro Kourí” (Cuba)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -6739,19 +6764,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Instituto de Medicina Tropical “Pedro Kourí”</t>
+          <t>Bernhard Nocht Institute for Tropical Medicine</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6766,7 +6791,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6792,12 +6817,12 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Yanisley Martínez López, Instituto de Medicina Tropical “Pedro Kourí” (Cuba)</t>
+          <t>In 2024, ITM junior researcher and PhD student Johanna Bouckaert attended a training at the Bernhard Nocht Institute for Tropical Medicine (BNITM) in Hamburg, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -6807,19 +6832,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bernhard Nocht Institute for Tropical Medicine (BNITM)</t>
+          <t>Ecodevelopment</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6829,7 +6854,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6865,7 +6890,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>In 2024, ITM junior researcher and PhD student Johanna Bouckaert attended a training at the Bernhard Nocht Institute for Tropical Medicine (BNITM) in Hamburg, with the support of an Erasmus+ mobility grant.</t>
+          <t>From 6 to 17 July 2026, Stien Vereecken and Emma Vandenberghe, two ITM scientists from the Unit of Entomology, participated in a specialised training programme at Ecodevelopment in Greece, with the support of an Erasmus+ staff mobility grant.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6875,19 +6900,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ecodevelopment</t>
+          <t>Goethe University</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6897,7 +6922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6933,7 +6958,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>From 6 to 17 July 2026, Stien Vereecken and Emma Vandenberghe, two ITM scientists from the Unit of Entomology, participated in a specialised training programme at Ecodevelopment in Greece, with the support of an Erasmus+ staff mobility grant.</t>
+          <t>From 1 to 5 July 2024, PhD candidate Adwine Vanslembrouck had the opportunity to follow a field training with Goethe University in Frankfurt, supported by an Erasmus+ mobility grant</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6943,14 +6968,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Goethe University</t>
+          <t>Institute of International Health Charité</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6970,7 +6995,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -7001,7 +7026,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>From 1 to 5 July 2024, PhD candidate Adwine Vanslembrouck had the opportunity to follow a field training with Goethe University in Frankfurt, supported by an Erasmus+ mobility grant</t>
+          <t>From 3 to 14 June 2024, ITM junior researcher and part-time MPH student Luciana Lepore followed a tropEd-accredited training on Qualitative Research Methods and Data Management at the Institute of International Health Charité in Berlin, supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7011,19 +7036,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Institute of International Health Charité</t>
+          <t>McGill Summer Institute</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7038,7 +7063,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -7069,7 +7094,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>From 3 to 14 June 2024, ITM junior researcher and part-time MPH student Luciana Lepore followed a tropEd-accredited training on Qualitative Research Methods and Data Management at the Institute of International Health Charité in Berlin, supported by an Erasmus+ mobility grant.</t>
+          <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7079,19 +7104,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>McGill Summer Institute</t>
+          <t>National Reference Center for Rickettsioses</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7106,7 +7131,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -7137,7 +7162,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
+          <t>From 4 to 15 March 2024, ITM PhD student Carl Boodman participated in a training programme at the National Reference Center for Rickettsioses (NRCR) in Marseille, France, affiliated with Aix-Marseille University. His participation was supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -7147,14 +7172,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>National Reference Center for Rickettsioses (NRCR)</t>
+          <t>Aix-Marseille University</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7174,7 +7199,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7215,19 +7240,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aix-Marseille University</t>
+          <t>AP Hogeschool Antwerpen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7237,12 +7262,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>college</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7268,12 +7293,12 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>From 4 to 15 March 2024, ITM PhD student Carl Boodman participated in a training programme at the National Reference Center for Rickettsioses (NRCR) in Marseille, France, affiliated with Aix-Marseille University. His participation was supported by an Erasmus+ mobility grant.</t>
+          <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -7283,14 +7308,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AP Hogeschool Antwerpen</t>
+          <t>Erasmushogeschool Brussel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7351,14 +7376,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Erasmushogeschool Brussel</t>
+          <t>Antwerp Maritime Academy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7419,14 +7444,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Antwerp Maritime Academy</t>
+          <t>HOGENT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7487,14 +7512,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HOGENT</t>
+          <t>Howest</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7555,14 +7580,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Howest</t>
+          <t>Arteveldehogeschool</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7623,14 +7648,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Arteveldehogeschool</t>
+          <t>Vrije Universiteit Brussel</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7645,7 +7670,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7691,14 +7716,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vrije Universiteit Brussel</t>
+          <t>Universiteit Antwerpen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7759,14 +7784,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Universiteit Antwerpen</t>
+          <t>Universiteit Gent</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7827,21 +7852,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Universiteit Gent</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+          <t>tropEd</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>International</t>
@@ -7849,12 +7870,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -7880,12 +7901,12 @@
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
+          <t>Do you want to follow a (blended) course at one of the tropEd partner institutions? Or would you like to do a traineeship at one of ITM’s international partner institutions to strengthen your lab skills or to collect field data for your thesis?</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -7895,19 +7916,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fonds Wetenschappelijk Onderzoek Vlaanderen</t>
+          <t>McGill Summer Institute in Montréal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7917,12 +7938,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -7948,12 +7969,12 @@
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Vier ITG-onderzoekers ontvangen postdoctoraal mandaat van het Fonds Wetenschappelijk Onderzoek Vlaanderen</t>
+          <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -7963,7 +7984,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
@@ -7973,11 +7994,7 @@
           <t>Nova Academy</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>International</t>
@@ -8016,12 +8033,12 @@
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Nova Academy groeit uit tot een breed partnerschap van tien hogeronderwijsinstellingen en versterkt de levenslanglerenmindset in Vlaanderen</t>
+          <t>Op vrijdag 29 mei 2026 vond de officiële lancering van de vernieuwde Nova Academy plaats aan de Erasmushogeschool in Brussel. Wat in 2021 begon als een samenwerking tussen drie universiteiten, is uitgegroeid tot een sterk partnerschap van tien Vlaamse instellingen voor hoger onderwijs die samen inzetten op levenslang leren. Ook het Instituut voor Tropische Geneeskunde (ITG) maakt deel uit van de samenwerking. Algemeen beheerder Ann Peters vertegenwoordigde het ITG tijdens dit feestelijke eveneme</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -8031,19 +8048,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bernhard Nocht Institute for Tropical Medicine</t>
+          <t>Belgische Directoraat-Generaal voor Ontwikkelingssamenwerking en Humanitaire Hulp (DGD)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8053,12 +8070,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -8084,12 +8101,12 @@
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>In 2024, ITM junior researcher and PhD student Johanna Bouckaert attended a training at the Bernhard Nocht Institute for Tropical Medicine (BNITM) in Hamburg, with the support of an Erasmus+ mobility grant.</t>
+          <t>Het ITG werkt samen met 24 partners, verspreid over drie continenten. De partnerschappen worden gefinancierd met een vijfjarensubsidie van het Belgische Directoraat-Generaal voor Ontwikkelingssamenwerking en Humanitaire Hulp (DGD). De Vlaamse Regering financiert daarnaast nog twee partnerschappen in Mozambique.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -8099,19 +8116,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tropEd</t>
+          <t>Vlaamse Regering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8121,7 +8138,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -8152,12 +8169,12 @@
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Do you want to follow a (blended) course at one of the tropEd partner institutions? Or would you like to do a traineeship at one of ITM’s international partner institutions to strengthen your lab skills or to collect field data for your thesis?</t>
+          <t>Het ITG werkt samen met 24 partners, verspreid over drie continenten. De partnerschappen worden gefinancierd met een vijfjarensubsidie van het Belgische Directoraat-Generaal voor Ontwikkelingssamenwerking en Humanitaire Hulp (DGD). De Vlaamse Regering financiert daarnaast nog twee partnerschappen in Mozambique.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -8167,21 +8184,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UGent</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+          <t>Be-cause Health</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>International</t>
@@ -8189,7 +8202,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -8220,12 +8233,12 @@
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
+          <t>Be-cause Health</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -8235,21 +8248,17 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Universitair Ziekenhuis Antwerpen (UZA)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+          <t>LINQED</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>International</t>
@@ -8257,7 +8266,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -8288,12 +8297,12 @@
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl/contact</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Universitair Ziekenhuis Antwerpen (UZA)</t>
+          <t>LINQED</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -8303,29 +8312,25 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Armauer Hansen Research Institute</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Emerging Voices for Global Health</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -8356,12 +8361,12 @@
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>In de aanloop naar het 66e ITG-colloquium bespreken wetenschappelijke leiders prof. dr. Johan van Griensven (Instituut voor Tropische Geneeskunde) en dr. Endalamaw Gadisa (Armauer Hansen Research Institute) waarom mobiliteit een cruciale rol speelt in het begrijpen van infectieziekten en waarom onderzoekers verder moeten kijken dan hun eigen discipline.</t>
+          <t>Emerging Voices for Global Health</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -8371,29 +8376,25 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Africalia</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Fiabel</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -8408,7 +8409,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -8424,44 +8425,40 @@
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Om te blijven reflecteren op ons koloniaal erfgoed en onze institutionele geschiedenis, lanceert het ITG een artist residency in samenwerking met Africalia. We zoeken een kunstenaar uit de Democratische Republiek Congo om kritisch te reflecteren op de kunstwerken van Fernand Allard l'Olivier en de bredere vragen die ze oproepen over institutioneel geheugen, koloniaal erfgoed en de blijvende impact van kolonialisme op het heden. Stel je kandidaat vóór 20 augustus.</t>
+          <t>Fiabel</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>quote not found on the cited page</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>European Society of Mycobacteriology</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>International Health Policies</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -8492,12 +8489,12 @@
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Professor Bouke de Jong ontvangt de Gardner Middlebrook Award 2026 van de European Society of Mycobacteriology</t>
+          <t>International Health Policies</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -8507,29 +8504,25 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PNTTE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>UAntwerpen</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -8544,64 +8537,61 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.itg.be/nl</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
+          <t>UAntwerpen (TBD)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>praxisnetwork.eu</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Bernhard Nocht Institute for Tropical Medicine (BNITM)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8611,51 +8601,48 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="J41" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>http://www.praxisnetwork.eu/</t>
+          <t>In 2024, ITM junior researcher and PhD student Johanna Bouckaert attended a training at the Bernhard Nocht Institute for Tropical Medicine (BNITM) in Hamburg, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Batman Universitesi</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Goethe University in Frankfurt</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>Country not stated</t>
@@ -8668,7 +8655,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8678,51 +8665,48 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Batman Universitesi</t>
+          <t>From 1 to 5 July 2024, PhD candidate Adwine Vanslembrouck had the opportunity to follow a field training with Goethe University in Frankfurt, supported by an Erasmus+ mobility grant</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COFAC</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Institute of International Health Charité in Berlin</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>Country not stated</t>
@@ -8735,7 +8719,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8745,51 +8729,48 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>COFAC</t>
+          <t>From 3 to 14 June 2024, ITM junior researcher and part-time MPH student Luciana Lepore followed a tropEd-accredited training on Qualitative Research Methods and Data Management at the Institute of International Health Charité in Berlin, supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CULS Prague</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>UGent</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>Country not stated</t>
@@ -8802,7 +8783,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8812,51 +8793,48 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>CULS Prague</t>
+          <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETEA</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>National Reference Center for Rickettsioses (NRCR)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>Country not stated</t>
@@ -8864,12 +8842,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8879,51 +8857,48 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ETEA</t>
+          <t>From 4 to 15 March 2024, ITM PhD student Carl Boodman participated in a training programme at the National Reference Center for Rickettsioses (NRCR) in Marseille, France, affiliated with Aix-Marseille University. His participation was supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fachhochschule des Mittelstandes</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Erasmushogeschool</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Country not stated</t>
@@ -8931,7 +8906,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>college</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -8946,44 +8921,45 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Fachhochschule des Mittelstandes</t>
+          <t>Op vrijdag 29 mei 2026 vond de officiële lancering van de vernieuwde Nova Academy plaats aan de Erasmushogeschool in Brussel. Wat in 2021 begon als een samenwerking tussen drie universiteiten, is uitgegroeid tot een sterk partnerschap van tien Vlaamse instellingen voor hoger onderwijs die samen inzetten op levenslang leren. Ook het Instituut voor Tropische Geneeskunde (ITG) maakt deel uit van de samenwerking. Algemeen beheerder Ann Peters vertegenwoordigde het ITG tijdens dit feestelijke eveneme</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HEL</t>
+          <t>PNTTE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8993,12 +8969,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -9028,12 +9004,12 @@
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>HEL</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -9050,7 +9026,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IPB</t>
+          <t>praxisnetwork.eu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9060,12 +9036,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -9095,12 +9071,12 @@
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>IPB</t>
+          <t>http://www.praxisnetwork.eu/</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -9117,7 +9093,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kirklareli University</t>
+          <t>Batman Universitesi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9167,7 +9143,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Kirklareli University</t>
+          <t>Batman Universitesi</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -9184,7 +9160,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Loyola University</t>
+          <t>COFAC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9234,7 +9210,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Loyola University</t>
+          <t>COFAC</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -9251,7 +9227,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
+          <t>CULS Prague</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9301,7 +9277,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
+          <t>CULS Prague</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -9318,7 +9294,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Paderborn University</t>
+          <t>ETEA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9368,7 +9344,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Paderborn University</t>
+          <t>ETEA</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -9385,7 +9361,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Panepistimio Thessalias</t>
+          <t>Fachhochschule des Mittelstandes</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9435,7 +9411,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Panepistimio Thessalias</t>
+          <t>Fachhochschule des Mittelstandes</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -9452,7 +9428,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PEGASO</t>
+          <t>HEL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9502,7 +9478,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>PEGASO</t>
+          <t>HEL</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -9519,7 +9495,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sia Biznesa Augstskola Turiba</t>
+          <t>IPB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9569,7 +9545,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Sia Biznesa Augstskola Turiba</t>
+          <t>IPB</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -9586,7 +9562,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SMK Aukštoji Mokykla</t>
+          <t>Kirklareli University</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9636,7 +9612,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>SMK Aukštoji Mokykla</t>
+          <t>Kirklareli University</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -9653,7 +9629,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TSI</t>
+          <t>Loyola University</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9703,7 +9679,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>TSI</t>
+          <t>Loyola University</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -9720,7 +9696,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>UFUK University</t>
+          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9770,7 +9746,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>UFUK University</t>
+          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -9787,7 +9763,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Universidad de Alicante</t>
+          <t>Paderborn University</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9837,7 +9813,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Universidad de Alicante</t>
+          <t>Paderborn University</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -9854,7 +9830,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Universidad de la Laguna</t>
+          <t>Panepistimio Thessalias</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9904,7 +9880,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Universidad de la Laguna</t>
+          <t>Panepistimio Thessalias</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9921,7 +9897,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>University of Žilina</t>
+          <t>PEGASO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9971,7 +9947,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>University of Žilina</t>
+          <t>PEGASO</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9988,7 +9964,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Univerza v Mariboru</t>
+          <t>Sia Biznesa Augstskola Turiba</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10038,7 +10014,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Univerza v Mariboru</t>
+          <t>Sia Biznesa Augstskola Turiba</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -10055,7 +10031,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Veleučilište Aspira</t>
+          <t>SMK Aukštoji Mokykla</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10105,7 +10081,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Veleučilište Aspira</t>
+          <t>SMK Aukštoji Mokykla</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -10122,7 +10098,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WU Wien</t>
+          <t>TSI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10172,7 +10148,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>WU Wien</t>
+          <t>TSI</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -10189,7 +10165,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Uniwersytet Stanforda</t>
+          <t>UFUK University</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10234,12 +10210,12 @@
       </c>
       <c r="J65" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Dyrektor Instytutu Informatyki i Innowacyjnych technologii. Zaklasyfikowany jako top2% najbardziej wpływowych ludzie w świecie nauki przez Uniwersytet Stanforda</t>
+          <t>UFUK University</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -10256,7 +10232,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PKN Orlen</t>
+          <t>Universidad de Alicante</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10271,7 +10247,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -10301,12 +10277,12 @@
       </c>
       <c r="J66" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>Universidad de Alicante</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -10323,7 +10299,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KGHM</t>
+          <t>Universidad de la Laguna</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10338,7 +10314,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -10368,12 +10344,12 @@
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>Universidad de la Laguna</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -10390,7 +10366,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Grupa Azoty</t>
+          <t>University of Žilina</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10405,7 +10381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -10435,12 +10411,12 @@
       </c>
       <c r="J68" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>University of Žilina</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -10457,7 +10433,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PKS Ryki</t>
+          <t>Univerza v Mariboru</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10472,7 +10448,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -10502,12 +10478,12 @@
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
+          <t>Univerza v Mariboru</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -10524,7 +10500,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cewar Lublin</t>
+          <t>Veleučilište Aspira</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -10539,7 +10515,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -10569,12 +10545,12 @@
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
+          <t>Veleučilište Aspira</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -10591,7 +10567,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AIE</t>
+          <t>WU Wien</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10606,7 +10582,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -10641,7 +10617,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>AIE</t>
+          <t>WU Wien</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -10658,7 +10634,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ashina Records</t>
+          <t>Uniwersytet Stanforda</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10673,7 +10649,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -10703,12 +10679,12 @@
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Ashina Records</t>
+          <t>Dyrektor Instytutu Informatyki i Innowacyjnych technologii. Zaklasyfikowany jako top2% najbardziej wpływowych ludzie w świecie nauki przez Uniwersytet Stanforda</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -10725,7 +10701,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Axel Lugo</t>
+          <t>PKN Orlen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10740,7 +10716,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -10770,12 +10746,12 @@
       </c>
       <c r="J73" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Axel Lugo</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -10792,7 +10768,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BBCA</t>
+          <t>KGHM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10807,7 +10783,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -10837,12 +10813,12 @@
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>BBCA</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -10859,7 +10835,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Capture Models</t>
+          <t>Grupa Azoty</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10904,12 +10880,12 @@
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Capture Models</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -10926,7 +10902,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EELI</t>
+          <t>PKS Ryki</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10941,7 +10917,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -10971,12 +10947,12 @@
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>EELI</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -10993,7 +10969,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>Cewar Lublin</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -11008,7 +10984,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11038,12 +11014,12 @@
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -11060,7 +11036,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EureCons</t>
+          <t>AIE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -11075,7 +11051,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -11110,7 +11086,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>EureCons</t>
+          <t>AIE</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -11127,7 +11103,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FOLA nature</t>
+          <t>Ashina Records</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -11142,7 +11118,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -11177,7 +11153,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>FOLA nature</t>
+          <t>Ashina Records</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -11194,7 +11170,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Franziskus Spital</t>
+          <t>Axel Lugo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -11244,7 +11220,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Franziskus Spital</t>
+          <t>Axel Lugo</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -11261,7 +11237,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Galileo Progetti</t>
+          <t>BBCA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -11311,7 +11287,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Galileo Progetti</t>
+          <t>BBCA</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -11328,7 +11304,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>I am the best</t>
+          <t>Capture Models</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -11343,7 +11319,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11378,7 +11354,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>I am the best</t>
+          <t>Capture Models</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -11395,7 +11371,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Institute Perspectives</t>
+          <t>EELI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -11445,7 +11421,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Institute Perspectives</t>
+          <t>EELI</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -11462,7 +11438,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ShipCon</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -11477,7 +11453,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -11512,7 +11488,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ShipCon</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -11529,7 +11505,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Silifke Diyaliz</t>
+          <t>EureCons</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -11544,7 +11520,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -11579,7 +11555,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Silifke Diyaliz</t>
+          <t>EureCons</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -11596,7 +11572,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SPEL</t>
+          <t>FOLA nature</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -11646,7 +11622,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>SPEL</t>
+          <t>FOLA nature</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -11663,7 +11639,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>Franziskus Spital</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -11713,7 +11689,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>Franziskus Spital</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -11730,7 +11706,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Universal mobility</t>
+          <t>Galileo Progetti</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -11780,7 +11756,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Universal mobility</t>
+          <t>Galileo Progetti</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -11797,7 +11773,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>UX Solutions</t>
+          <t>I am the best</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -11812,7 +11788,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -11847,7 +11823,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>UX Solutions</t>
+          <t>I am the best</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -11864,7 +11840,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Amadeus Association</t>
+          <t>Institute Perspectives</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11914,7 +11890,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Amadeus Association</t>
+          <t>Institute Perspectives</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -11931,7 +11907,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APDI</t>
+          <t>ShipCon</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11946,7 +11922,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -11981,7 +11957,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>APDI</t>
+          <t>ShipCon</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -11998,7 +11974,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>APSU</t>
+          <t>Silifke Diyaliz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -12048,7 +12024,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>APSU</t>
+          <t>Silifke Diyaliz</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -12065,7 +12041,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Arte Psy Association</t>
+          <t>SPEL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -12115,7 +12091,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Arte Psy Association</t>
+          <t>SPEL</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -12132,7 +12108,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Aspire-Igen LTD</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -12147,7 +12123,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12182,7 +12158,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Aspire-Igen LTD</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -12199,7 +12175,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Aviteum</t>
+          <t>Universal mobility</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -12249,7 +12225,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Aviteum</t>
+          <t>Universal mobility</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -12266,7 +12242,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cardet</t>
+          <t>UX Solutions</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -12281,7 +12257,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12316,7 +12292,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Cardet</t>
+          <t>UX Solutions</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -12333,7 +12309,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ECTE</t>
+          <t>Amadeus Association</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -12383,7 +12359,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>ECTE</t>
+          <t>Amadeus Association</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -12400,7 +12376,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Eduforma</t>
+          <t>APDI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -12450,7 +12426,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Eduforma</t>
+          <t>APDI</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -12467,7 +12443,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Expert Psy</t>
+          <t>APSU</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -12517,7 +12493,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Expert Psy</t>
+          <t>APSU</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -12534,7 +12510,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FFE</t>
+          <t>Arte Psy Association</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -12584,7 +12560,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>FFE</t>
+          <t>Arte Psy Association</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -12601,7 +12577,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>Aspire-Igen LTD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -12616,7 +12592,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -12651,7 +12627,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>Aspire-Igen LTD</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -12668,7 +12644,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Forpro Creteil</t>
+          <t>Aviteum</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -12718,7 +12694,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Forpro Creteil</t>
+          <t>Aviteum</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -12735,7 +12711,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Fuitec</t>
+          <t>Cardet</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12785,7 +12761,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Fuitec</t>
+          <t>Cardet</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -12802,7 +12778,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Fundatia Danis</t>
+          <t>ECTE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12852,7 +12828,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Fundatia Danis</t>
+          <t>ECTE</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -12869,7 +12845,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Eduforma</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12919,7 +12895,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Eduforma</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -12936,7 +12912,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Innogate to Europe</t>
+          <t>Expert Psy</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12986,7 +12962,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Innogate to Europe</t>
+          <t>Expert Psy</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -13003,7 +12979,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Innova SRL</t>
+          <t>FFE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -13018,7 +12994,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -13053,7 +13029,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Innova SRL</t>
+          <t>FFE</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -13070,7 +13046,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Innovation Frontiers</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -13120,7 +13096,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Innovation Frontiers</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -13137,7 +13113,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ITD</t>
+          <t>Forpro Creteil</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -13187,7 +13163,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>ITD</t>
+          <t>Forpro Creteil</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -13204,7 +13180,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Joudg "Breshia"</t>
+          <t>Fuitec</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -13254,7 +13230,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Joudg "Breshia"</t>
+          <t>Fuitec</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -13271,7 +13247,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Peipsi CTC</t>
+          <t>Fundatia Danis</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -13321,7 +13297,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Peipsi CTC</t>
+          <t>Fundatia Danis</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -13338,7 +13314,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Personnel Training</t>
+          <t>Idea</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13388,7 +13364,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Personnel Training</t>
+          <t>Idea</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -13405,7 +13381,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Prios</t>
+          <t>Innogate to Europe</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13455,7 +13431,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Prios</t>
+          <t>Innogate to Europe</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -13472,7 +13448,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Proficio Skopje</t>
+          <t>Innova SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -13487,7 +13463,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13522,7 +13498,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Proficio Skopje</t>
+          <t>Innova SRL</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -13539,7 +13515,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Innovation Frontiers</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13589,7 +13565,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Innovation Frontiers</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -13606,7 +13582,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SIPOB</t>
+          <t>ITD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13656,7 +13632,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>SIPOB</t>
+          <t>ITD</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -13673,7 +13649,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VekstTorget</t>
+          <t>Joudg "Breshia"</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13723,7 +13699,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>VekstTorget</t>
+          <t>Joudg "Breshia"</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -13740,7 +13716,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Weltgewandt</t>
+          <t>Peipsi CTC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13790,7 +13766,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Weltgewandt</t>
+          <t>Peipsi CTC</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -13807,12 +13783,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Muurame Lukio</t>
+          <t>Personnel Training</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13822,7 +13798,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -13842,22 +13818,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J119" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>🇫🇮 a finn Muurame Lukio képviselői</t>
+          <t>Personnel Training</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -13867,19 +13843,19 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IES Álvaro Cunqueiro</t>
+          <t>Prios</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13889,7 +13865,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -13909,22 +13885,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J120" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES Álvaro Cunqueiro (Vigo) képviselője</t>
+          <t>Prios</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -13934,19 +13910,19 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IES Isabel de Villena</t>
+          <t>Proficio Skopje</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13956,7 +13932,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -13976,22 +13952,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J121" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES Isabel de Villena (Valencia) képviselője</t>
+          <t>Proficio Skopje</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -14001,19 +13977,19 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IES El Batán</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -14023,12 +13999,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -14043,22 +14019,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J122" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES El Batán (Gran Canaria) diákcsoportja és kísérői</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -14068,19 +14044,19 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Csutak Vilmos Pedagógusok Háza</t>
+          <t>SIPOB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -14110,22 +14086,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J123" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>🇷🇴 a Csutak Vilmos Pedagógusok Háza pedagógusai Erdélyből</t>
+          <t>SIPOB</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -14135,19 +14111,19 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ALFMED</t>
+          <t>VekstTorget</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -14157,12 +14133,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -14177,22 +14153,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J124" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>FRANCIAORSZÁG – PERPIGNAN – ALFMED (2018. március 19-26.)</t>
+          <t>VekstTorget</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -14202,19 +14178,19 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Notre Dame De Bon Secours Katolikus Magán Középiskola</t>
+          <t>Weltgewandt</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14224,7 +14200,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -14244,22 +14220,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J125" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Első utunk a Notre Dame De Bon Secours Katolikus Magán Középiskolába vezetett, amely egy patinás, 19. századi épületegyüttesben található Perpignan óvárosában. Az iskolát 1871-ben alapították, 144 éves múltra tekint vissza és jelenleg összesen 1500 diák oktatásáról és neveléséről gondoskodik középiskolai és érettségi utáni felnőtt – képzés keretében. Az iskola látogatásakor az intézmény vezetői, igazgatója és igazgató helyettese, egy angol tanár és a pályázatfelelős, illetve az intézményben tanu</t>
+          <t>Weltgewandt</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -14269,19 +14245,19 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lycee Christian Bourquin VET School</t>
+          <t>Muurame Lukio</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14321,12 +14297,12 @@
       </c>
       <c r="J126" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Következő látogatásunkat a dél –franciaországi régió egyik legmodernebb közép és főiskolájában – Lycee Christian Bourquin VET School – ban tettük.</t>
+          <t>🇫🇮 a finn Muurame Lukio képviselői</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -14343,12 +14319,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Irish Education Partners</t>
+          <t>IES Álvaro Cunqueiro</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14358,12 +14334,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14388,12 +14364,12 @@
       </c>
       <c r="J127" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>ÍRORSZÁG – DUBLIN – Irish Educaton Partners (2018. március 7-14.)</t>
+          <t>🇪🇸 az IES Álvaro Cunqueiro (Vigo) képviselője</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -14410,12 +14386,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sedat Karan Anadolu Lisesi</t>
+          <t>IES Isabel de Villena</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14430,7 +14406,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14455,12 +14431,12 @@
       </c>
       <c r="J128" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2025 májusában lehetőségem nyílt arra, hogy Erasmus+ mobilitás keretében szakmai látogatáson (job shadowing) vegyek részt Törökországban. A Bursa kerülethez tartozó Mustafakemalpaşa település Sedat Karan Anadolu Lisesi […]</t>
+          <t>🇪🇸 az IES Isabel de Villena (Valencia) képviselője</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -14477,12 +14453,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Hannah-Arendt Gimnázium</t>
+          <t>IES El Batán</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14497,7 +14473,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14522,12 +14498,12 @@
       </c>
       <c r="J129" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>ERASMUS+ job-shadowing mobilitási tevékenység Egy Erasmus-programnak köszönhetően február elején egy hetet tölthettem Berlin városában, a Hannah-Arendt Gimnáziumban. Célom az volt, hogy megismerjem a német oktatási rendszer […]</t>
+          <t>🇪🇸 az IES El Batán (Gran Canaria) diákcsoportja és kísérői</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -14544,12 +14520,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mankolan koulu</t>
+          <t>Csutak Vilmos Pedagógusok Háza</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14559,12 +14535,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14589,12 +14565,12 @@
       </c>
       <c r="J130" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026. január 26. és február 1. között Erasmus+ mobilitás keretében lehetőségem nyílt szakmai job shadowing programon részt venni a finnországi Jyväskylä városában működő Mankolan koulu általános […]</t>
+          <t>🇷🇴 a Csutak Vilmos Pedagógusok Háza pedagógusai Erdélyből</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -14611,12 +14587,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Farel College</t>
+          <t>ALFMED</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14656,12 +14632,12 @@
       </c>
       <c r="J131" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Helyszín: Amersfoort, Farel CollegeIdőszak: 2025.november 17-21. Amersfoorti tartózkodásom legnagyobb élménye a holland iskolai rendszerbe való betekintési lehetőség volt. A rendszer ott is sérülékeny, és sok ponton […]</t>
+          <t>FRANCIAORSZÁG – PERPIGNAN – ALFMED (2018. március 19-26.)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -14678,12 +14654,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Organización de Estados Iberoamericanos (OEI)</t>
+          <t>Notre Dame De Bon Secours Katolikus Magán Középiskola</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14693,7 +14669,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -14713,22 +14689,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>r031</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ESCUELA SUPERIOR DE ARTE DRAMÁTICO DE CASTILLA</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J132" s="1" t="inlineStr">
         <is>
-          <t>https://www.educa.jcyl.es/profesorado/en/internacionalizacion-educacion-escolar/cooperacion-portugal</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Además, la Dirección General de Innovación y Formación del Profesorado trabaja con la Organización de Estados Iberoamericanos (OEI) en la puesta en marca de actuaciones de innovación educativa en cooperación con las autoridades lusas.</t>
+          <t>Első utunk a Notre Dame De Bon Secours Katolikus Magán Középiskolába vezetett, amely egy patinás, 19. századi épületegyüttesben található Perpignan óvárosában. Az iskolát 1871-ben alapították, 144 éves múltra tekint vissza és jelenleg összesen 1500 diák oktatásáról és neveléséről gondoskodik középiskolai és érettségi utáni felnőtt – képzés keretében. Az iskola látogatásakor az intézmény vezetői, igazgatója és igazgató helyettese, egy angol tanár és a pályázatfelelős, illetve az intézményben tanu</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -14738,14 +14714,14 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-10-04T06:59:23Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Académie des César</t>
+          <t>Lycee Christian Bourquin VET School</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14760,7 +14736,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -14775,49 +14751,49 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J133" s="1" t="inlineStr">
         <is>
-          <t>https://ad-education.com/academie-des-cesar-lecv-partenaire-des-nuits-en-or/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Académie des César – L’ECV, partenaire des Nuits en Or</t>
+          <t>Következő látogatásunkat a dél –franciaországi régió egyik legmodernebb közép és főiskolájában – Lycee Christian Bourquin VET School – ban tettük.</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Maddy Keynote</t>
+          <t>Irish Education Partners</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14832,7 +14808,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14842,49 +14818,49 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J134" s="1" t="inlineStr">
         <is>
-          <t>https://ad-education.com/ecv-partenaire-la-edition-la-maddy-keynote-mkn23/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>L’ECV, partenaire de la 7e édition de la Maddy Keynote – MKN23 !</t>
+          <t>ÍRORSZÁG – DUBLIN – Irish Educaton Partners (2018. március 7-14.)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EDC</t>
+          <t>Sedat Karan Anadolu Lisesi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -14899,7 +14875,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -14909,49 +14885,49 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J135" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>EDC</t>
+          <t>2025 májusában lehetőségem nyílt arra, hogy Erasmus+ mobilitás keretében szakmai látogatáson (job shadowing) vegyek részt Törökországban. A Bursa kerülethez tartozó Mustafakemalpaşa település Sedat Karan Anadolu Lisesi […]</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ECV</t>
+          <t>Hannah-Arendt Gimnázium</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -14966,7 +14942,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14976,49 +14952,49 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J136" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>ECV</t>
+          <t>ERASMUS+ job-shadowing mobilitási tevékenység Egy Erasmus-programnak köszönhetően február elején egy hetet tölthettem Berlin városában, a Hannah-Arendt Gimnáziumban. Célom az volt, hogy megismerjem a német oktatási rendszer […]</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IAAD</t>
+          <t>Mankolan koulu</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15033,7 +15009,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -15043,49 +15019,49 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J137" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>IAAD</t>
+          <t>2026. január 26. és február 1. között Erasmus+ mobilitás keretében lehetőségem nyílt szakmai job shadowing programon részt venni a finnországi Jyväskylä városában működő Mankolan koulu általános […]</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Accademia Italiana</t>
+          <t>Farel College</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15100,7 +15076,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -15110,44 +15086,44 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J138" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Accademia Italiana</t>
+          <t>Helyszín: Amersfoort, Farel CollegeIdőszak: 2025.november 17-21. Amersfoorti tartózkodásom legnagyobb élménye a holland iskolai rendszerbe való betekintési lehetőség volt. A rendszer ott is sérülékeny, és sok ponton […]</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CEV</t>
+          <t>Organización de Estados Iberoamericanos (OEI)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -15162,7 +15138,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -15177,49 +15153,49 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r031</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>ESCUELA SUPERIOR DE ARTE DRAMÁTICO DE CASTILLA</t>
         </is>
       </c>
       <c r="J139" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://www.educa.jcyl.es/profesorado/en/internacionalizacion-educacion-escolar/cooperacion-portugal</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>CEV</t>
+          <t>Además, la Dirección General de Innovación y Formación del Profesorado trabaja con la Organización de Estados Iberoamericanos (OEI) en la puesta en marca de actuaciones de innovación educativa en cooperación con las autoridades lusas.</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:59:23Z</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CES</t>
+          <t>Académie des César</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15229,7 +15205,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -15259,17 +15235,17 @@
       </c>
       <c r="J140" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://ad-education.com/academie-des-cesar-lecv-partenaire-des-nuits-en-or/</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>CES</t>
+          <t>Académie des César – L’ECV, partenaire des Nuits en Or</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -15281,12 +15257,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Barreira Arte y Diseño</t>
+          <t>Maddy Keynote</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15296,7 +15272,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -15326,17 +15302,17 @@
       </c>
       <c r="J141" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://ad-education.com/ecv-partenaire-la-edition-la-maddy-keynote-mkn23/</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Barreira Arte y Diseño</t>
+          <t>L’ECV, partenaire de la 7e édition de la Maddy Keynote – MKN23 !</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -15348,7 +15324,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Media University</t>
+          <t>EDC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -15398,12 +15374,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Media University</t>
+          <t>EDC</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -15415,7 +15391,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EAC</t>
+          <t>ECV</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -15465,12 +15441,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>EAC</t>
+          <t>ECV</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -15482,7 +15458,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>École Supérieure du Parfum</t>
+          <t>IAAD</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -15532,12 +15508,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>École Supérieure du Parfum</t>
+          <t>IAAD</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -15549,7 +15525,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>Accademia Italiana</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -15599,12 +15575,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>Accademia Italiana</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -15616,7 +15592,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ESD</t>
+          <t>CEV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -15666,12 +15642,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>ESD</t>
+          <t>CEV</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -15683,7 +15659,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IIM</t>
+          <t>CES</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15733,12 +15709,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>IIM</t>
+          <t>CES</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -15750,7 +15726,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EMLV</t>
+          <t>Barreira Arte y Diseño</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15800,12 +15776,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>EMLV</t>
+          <t>Barreira Arte y Diseño</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -15817,7 +15793,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ESILV</t>
+          <t>Media University</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -15867,12 +15843,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>ESILV</t>
+          <t>Media University</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -15884,22 +15860,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ALMA</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -15919,93 +15895,562 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>r033</t>
+          <t>r032</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>UNIVERSITE GRENOBLE ALPES</t>
+          <t>GROUPE EAC - ING</t>
         </is>
       </c>
       <c r="J150" s="1" t="inlineStr">
         <is>
-          <t>https://www.univ-grenoble-alpes.fr/</t>
+          <t>https://en.ad-education.com/</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Un programme international majeur d’observations de très jeunes étoiles, dans lequel sont impliqués des scientifiques de l’Institut de planétologie et d'astrophysique de Grenoble, livre ses premiers résultats. Grâce aux observations du réseau de radiotélescopes ALMA au Chili, l’équipe scientifique a détecté des molécules et leurs traces là où elles étaient supposément rares, voire inexistantes.</t>
+          <t>EAC</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:16Z</t>
+          <t>2026-10-22T10:32:01Z</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>École Supérieure du Parfum</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J151" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>École Supérieure du Parfum</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J152" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ESD</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J153" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>ESD</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>IIM</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>IIM</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>EMLV</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J155" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>EMLV</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ESILV</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J156" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>ESILV</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ALMA</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>r033</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>UNIVERSITE GRENOBLE ALPES</t>
+        </is>
+      </c>
+      <c r="J157" s="1" t="inlineStr">
+        <is>
+          <t>https://www.univ-grenoble-alpes.fr/</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Un programme international majeur d’observations de très jeunes étoiles, dans lequel sont impliqués des scientifiques de l’Institut de planétologie et d'astrophysique de Grenoble, livre ses premiers résultats. Grâce aux observations du réseau de radiotélescopes ALMA au Chili, l’équipe scientifique a détecté des molécules et leurs traces là où elles étaient supposément rares, voire inexistantes.</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>Mobicoop</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr">
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>r033</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t>UNIVERSITE GRENOBLE ALPES</t>
         </is>
       </c>
-      <c r="J151" s="1" t="inlineStr">
+      <c r="J158" s="1" t="inlineStr">
         <is>
           <t>https://www.univ-grenoble-alpes.fr/stand-sur-la-transformation-ecologique-et-la-mobilite-valence-1808967.kjsp?RH=1769439721486</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="K158" t="inlineStr">
         <is>
           <t>Ce stand est aussi l'occasion de s'informer sur le lancement de "Covoit'UGA" en partenariat avec Mobicoop. Covoit'UGA est un espace de réservation de covoiturage dédié aux personnels et étudiants à l'Université Grenoble Alpes pour favoriser le covoiturage entre Grenoble et Valence. Un cours à donner ou à suivre ? Voyager en groupe !</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t>quote found on page</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t>2026-10-22T10:32:16Z</t>
         </is>
@@ -16163,6 +16608,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16174,7 +16626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16421,7 +16873,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hoofdgebouw</t>
+          <t>Instituut voor Tropische Geneeskunde</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16446,7 +16898,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Haal je exemplaar aan het onthaal in het hoofdgebouw (Nationalestraat 155, 2000 Antwerpen) of via Standaard Boekhandel.</t>
+          <t>Het Instituut voor Tropische Geneeskunde (ITG) in Antwerpen (België) zet zich sinds 1906 in voor de vooruitgang van wetenschap en gezondheid voor iedereen, via innovatief onderzoek, geavanceerd onderwijs, professionele medische dienstverlening en capaciteitsuitwisseling met partnerinstellingen in Afrika, Azië en Latijns-Amerika. Ons doel is de wereldwijde impact van ziekten en gezondheidsproblemen op bevolkingsgroepen te verminderen.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -16461,7 +16913,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
@@ -16479,105 +16931,104 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ITM Campus Rochus</t>
+          <t>Vestiging ITG-DRC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Democratische Republiek Congo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Aula Janssens, ITM Campus Rochus, Sint-Rochusstraat 43, 2000 Antwerp</t>
+          <t>Vestiging ITG-DRC</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>quote not found on the cited page</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>r007</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
-Escuela Superior de Arte Dramático de Valencia</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ITG-DRC</t>
+          <t>Uniwersytet WSEI w Lublinie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>main</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl/internationale-samenwerking</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Vestiging ITG-DRC</t>
+          <t>ul. Projektowa 4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:45Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
@@ -16594,7 +17045,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uniwersytet WSEI w Lublinie</t>
+          <t>Filia w Warszawie</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -16604,12 +17055,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Warsaw</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -16619,7 +17070,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ul. Projektowa 4</t>
+          <t>Filia w Warszawie</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -16641,42 +17092,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Filia w Warszawie</t>
+          <t>Európa 2000 Gimnázium</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Warsaw</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>main</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://europa2000.hu/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Filia w Warszawie</t>
+          <t>Európa 2000 Gimnázium - kéttannyelvű alternatív gimnázium</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -16691,34 +17142,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-04T06:48:54Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Európa 2000 Gimnázium</t>
+          <t>uniT Graz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Österreich</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Graz</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -16728,54 +17179,54 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/</t>
+          <t>https://www.uni-t.org/contact</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Európa 2000 Gimnázium - kéttannyelvű alternatív gimnázium</t>
+          <t>8010 Graz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-22T10:32:10Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r023</t>
+          <t>r033</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>UNIVERSITE GRENOBLE ALPES</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uniT Graz</t>
+          <t>Domaine universitaire</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Österreich</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Graz</t>
+          <t>Saint-Martin-d'Hères</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -16785,12 +17236,12 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>https://www.uni-t.org/contact</t>
+          <t>https://www.univ-grenoble-alpes.fr/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8010 Graz</t>
+          <t>Agglomération grenobloise, Agglomération valentinoise</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -16805,7 +17256,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:10Z</t>
+          <t>2026-10-22T10:32:16Z</t>
         </is>
       </c>
     </row>
@@ -16822,7 +17273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Domaine universitaire</t>
+          <t>Campus universitaire de Valence</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16832,12 +17283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saint-Martin-d'Hères</t>
+          <t>Valence</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -16861,63 +17312,6 @@
         </is>
       </c>
       <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:32:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>r033</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>UNIVERSITE GRENOBLE ALPES</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Campus universitaire de Valence</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Valence</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>branch</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>https://www.univ-grenoble-alpes.fr/</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Agglomération grenobloise, Agglomération valentinoise</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
         <is>
           <t>2026-10-22T10:32:16Z</t>
         </is>
@@ -16936,7 +17330,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16948,7 +17341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17082,12 +17475,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -17097,170 +17491,176 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Artur Grzesiak</t>
+          <t>Charlotte Morantin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>University Erasmus + Coordinator</t>
+          <t>ITM Education Office</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>artur.grzesiak@wsei.pl</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>+48 81 749 32 51</t>
-        </is>
-      </c>
+          <t>cmorantin@itg.be</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Uczelniany Koordynator Programu Erasmus+ ... Artur Grzesiak</t>
+          <t>Interested? Contact the ITM Education Office (Charlotte Morantin – cmorantin@itg.be &lt;cmorantin@itg.be&gt;) to discuss the existing possibilities.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Institutional Erasmus+ coordinator. Artur Grzesiak is explicitly named as the University Erasmus+ Coordinator.</t>
+          <t>Secretary / administration (last resort). Charlotte Morantin is a contact in the ITM Education Office handling outgoing staff mobility options.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>name, email found on page</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Szalánczy Gábor</t>
+          <t>Jared Howes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Erasmus+ Coordinator</t>
+          <t>Ethics and Compliance Officer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>jhowes@itg.be</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.itg.be/en/institutional-review-board</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Szalánczy Gábor ... ERASMUS+ Koordinátor – történelem tanár</t>
+          <t>Jared Howes (Ethics and Compliance Officer)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Institutional Erasmus+ coordinator. Szalánczy Gábor is explicitly identified as the Erasmus+ Coordinator for the institution.</t>
+          <t>Secretary / administration (last resort). Jared Howes is the Ethics and Compliance Officer.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>name, email found on page</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
+Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Papp András</t>
+          <t>Raffaella Ravinetto</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Chair of the Institutional Review Board</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>rravinetto@itg.be</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/</t>
+          <t>https://www.itg.be/en/institutional-review-board</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Papp András, igazgató</t>
+          <t>Raffaella Ravinetto (Chair)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Principal / director (no Erasmus contact found). Papp András is the director of the school and is involved in Erasmus+ mobility reporting.</t>
+          <t>Other role. Raffaella Ravinetto is the Chair of the Institutional Review Board.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
+          <t>name, email found on page</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>r023</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -17270,52 +17670,60 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Edith Zeier-Draxl</t>
+          <t>Artur Grzesiak</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Artistic Director</t>
+          <t>University Erasmus + Coordinator</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>artur.grzesiak@wsei.pl</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>+48 81 749 32 51</t>
+        </is>
+      </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://www.uni-t.org/team</t>
+          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Edith Zeier-Draxl ... Künstlerische Leitung</t>
+          <t>Uczelniany Koordynator Programu Erasmus+ ... Artur Grzesiak</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Principal / director (no Erasmus contact found). As the artistic director, she holds a leadership role within the organization.</t>
+          <t>Institutional Erasmus+ coordinator. Artur Grzesiak is explicitly named as the University Erasmus+ Coordinator.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>name found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -17325,12 +17733,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aïda Diab</t>
+          <t>Szalánczy Gábor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Executive Director of EAC ASFORED</t>
+          <t>Erasmus+ Coordinator</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -17338,27 +17746,192 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr">
         <is>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Szalánczy Gábor ... ERASMUS+ Koordinátor – történelem tanár</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Institutional Erasmus+ coordinator. Szalánczy Gábor is explicitly identified as the Erasmus+ Coordinator for the institution.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>cited page was not read by the fetcher (cannot check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>r018</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Europa 2000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Papp András</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://europa2000.hu/</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Papp András, igazgató</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Principal / director (no Erasmus contact found). Papp András is the director of the school and is involved in Erasmus+ mobility reporting.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>cited page was not read by the fetcher (cannot check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>r023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Edith Zeier-Draxl</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Artistic Director</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.uni-t.org/team</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Edith Zeier-Draxl ... Künstlerische Leitung</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Principal / director (no Erasmus contact found). As the artistic director, she holds a leadership role within the organization.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Aïda Diab</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Executive Director of EAC ASFORED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
           <t>https://en.ad-education.com/our-team/</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Aïda Diab ... Executive Director of EAC ASFORED</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Principal / director (no Erasmus contact found). Aïda Diab is the Executive Director of EAC, which is the institution in question.</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>name found on page</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -17370,6 +17943,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17381,7 +17957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18321,76 +18897,74 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r007</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
-Escuela Superior de Arte Dramático de Valencia</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Africalia</t>
+          <t>Artur Grzesiak</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Om te blijven reflecteren op ons koloniaal erfgoed en onze institutionele geschiedenis, lanceert het ITG een artist residency in samenwerking met Africalia. We zoeken een kunstenaar uit de Democratische Republiek Congo om kritisch te reflecteren op de kunstwerken van Fernand Allard l'Olivier en de bredere vragen die ze oproepen over institutioneel geheugen, koloniaal erfgoed en de blijvende impact van kolonialisme op het heden. Stel je kandidaat vóór 20 augustus.</t>
+          <t>Uczelniany Koordynator Programu Erasmus+ ... Artur Grzesiak</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>quote not found on the cited page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>r007</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
-Escuela Superior de Arte Dramático de Valencia</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>campus</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ITM Campus Rochus</t>
+          <t>Batman Universitesi</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aula Janssens, ITM Campus Rochus, Sint-Rochusstraat 43, 2000 Antwerp</t>
+          <t>Batman Universitesi</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>quote not found on the cited page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -18407,22 +18981,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Artur Grzesiak</t>
+          <t>COFAC</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Uczelniany Koordynator Programu Erasmus+ ... Artur Grzesiak</t>
+          <t>COFAC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -18449,7 +19023,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Batman Universitesi</t>
+          <t>CULS Prague</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -18459,7 +19033,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Batman Universitesi</t>
+          <t>CULS Prague</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -18486,7 +19060,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>COFAC</t>
+          <t>ETEA</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -18496,7 +19070,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COFAC</t>
+          <t>ETEA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -18523,7 +19097,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CULS Prague</t>
+          <t>Fachhochschule des Mittelstandes</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -18533,7 +19107,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CULS Prague</t>
+          <t>Fachhochschule des Mittelstandes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -18560,7 +19134,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ETEA</t>
+          <t>HEL</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -18570,7 +19144,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ETEA</t>
+          <t>HEL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -18597,7 +19171,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fachhochschule des Mittelstandes</t>
+          <t>IPB</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -18607,7 +19181,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fachhochschule des Mittelstandes</t>
+          <t>IPB</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -18634,7 +19208,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HEL</t>
+          <t>Kirklareli University</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -18644,7 +19218,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HEL</t>
+          <t>Kirklareli University</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -18671,7 +19245,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IPB</t>
+          <t>Loyola University</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -18681,7 +19255,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IPB</t>
+          <t>Loyola University</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -18708,7 +19282,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Kirklareli University</t>
+          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -18718,7 +19292,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kirklareli University</t>
+          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -18745,7 +19319,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Loyola University</t>
+          <t>Paderborn University</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -18755,7 +19329,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Loyola University</t>
+          <t>Paderborn University</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -18782,7 +19356,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
+          <t>Panepistimio Thessalias</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -18792,7 +19366,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
+          <t>Panepistimio Thessalias</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -18819,7 +19393,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paderborn University</t>
+          <t>PEGASO</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -18829,7 +19403,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paderborn University</t>
+          <t>PEGASO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -18856,7 +19430,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Panepistimio Thessalias</t>
+          <t>Sia Biznesa Augstskola Turiba</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -18866,7 +19440,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Panepistimio Thessalias</t>
+          <t>Sia Biznesa Augstskola Turiba</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -18893,7 +19467,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PEGASO</t>
+          <t>SMK Aukštoji Mokykla</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -18903,7 +19477,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PEGASO</t>
+          <t>SMK Aukštoji Mokykla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -18930,7 +19504,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sia Biznesa Augstskola Turiba</t>
+          <t>TSI</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -18940,7 +19514,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sia Biznesa Augstskola Turiba</t>
+          <t>TSI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -18967,7 +19541,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SMK Aukštoji Mokykla</t>
+          <t>UFUK University</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -18977,7 +19551,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SMK Aukštoji Mokykla</t>
+          <t>UFUK University</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -19004,7 +19578,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TSI</t>
+          <t>Universidad de Alicante</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -19014,7 +19588,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TSI</t>
+          <t>Universidad de Alicante</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -19041,7 +19615,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UFUK University</t>
+          <t>Universidad de la Laguna</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -19051,7 +19625,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UFUK University</t>
+          <t>Universidad de la Laguna</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -19078,7 +19652,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Universidad de Alicante</t>
+          <t>University of Žilina</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -19088,7 +19662,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universidad de Alicante</t>
+          <t>University of Žilina</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -19115,7 +19689,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Universidad de la Laguna</t>
+          <t>Univerza v Mariboru</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -19125,7 +19699,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universidad de la Laguna</t>
+          <t>Univerza v Mariboru</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -19152,7 +19726,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>University of Žilina</t>
+          <t>Veleučilište Aspira</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -19162,7 +19736,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>University of Žilina</t>
+          <t>Veleučilište Aspira</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -19189,7 +19763,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Univerza v Mariboru</t>
+          <t>WU Wien</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -19199,7 +19773,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Univerza v Mariboru</t>
+          <t>WU Wien</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -19226,17 +19800,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Veleučilište Aspira</t>
+          <t>Uniwersytet Stanforda</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Veleučilište Aspira</t>
+          <t>Dyrektor Instytutu Informatyki i Innowacyjnych technologii. Zaklasyfikowany jako top2% najbardziej wpływowych ludzie w świecie nauki przez Uniwersytet Stanforda</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -19263,17 +19837,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>WU Wien</t>
+          <t>PKN Orlen</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WU Wien</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -19300,7 +19874,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Uniwersytet Stanforda</t>
+          <t>KGHM</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -19310,7 +19884,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dyrektor Instytutu Informatyki i Innowacyjnych technologii. Zaklasyfikowany jako top2% najbardziej wpływowych ludzie w świecie nauki przez Uniwersytet Stanforda</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -19337,7 +19911,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PKN Orlen</t>
+          <t>Grupa Azoty</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -19374,7 +19948,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KGHM</t>
+          <t>PKS Ryki</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -19384,7 +19958,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -19411,7 +19985,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Grupa Azoty</t>
+          <t>Cewar Lublin</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -19421,7 +19995,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -19448,7 +20022,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PKS Ryki</t>
+          <t>PNTTE</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -19485,17 +20059,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cewar Lublin</t>
+          <t>AIE</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
+          <t>AIE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -19522,17 +20096,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PNTTE</t>
+          <t>Ashina Records</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
+          <t>Ashina Records</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -19559,7 +20133,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AIE</t>
+          <t>Axel Lugo</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -19569,7 +20143,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AIE</t>
+          <t>Axel Lugo</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -19596,7 +20170,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ashina Records</t>
+          <t>BBCA</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -19606,7 +20180,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ashina Records</t>
+          <t>BBCA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -19633,7 +20207,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Axel Lugo</t>
+          <t>Capture Models</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -19643,7 +20217,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Axel Lugo</t>
+          <t>Capture Models</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -19670,7 +20244,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BBCA</t>
+          <t>EELI</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -19680,7 +20254,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BBCA</t>
+          <t>EELI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -19707,7 +20281,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Capture Models</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -19717,7 +20291,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Capture Models</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -19744,7 +20318,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EELI</t>
+          <t>EureCons</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -19754,7 +20328,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>EELI</t>
+          <t>EureCons</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -19781,7 +20355,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>FOLA nature</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -19791,7 +20365,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>FOLA nature</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -19818,7 +20392,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EureCons</t>
+          <t>Franziskus Spital</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -19828,7 +20402,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>EureCons</t>
+          <t>Franziskus Spital</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -19855,7 +20429,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FOLA nature</t>
+          <t>Galileo Progetti</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -19865,7 +20439,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FOLA nature</t>
+          <t>Galileo Progetti</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -19892,7 +20466,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Franziskus Spital</t>
+          <t>I am the best</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -19902,7 +20476,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Franziskus Spital</t>
+          <t>I am the best</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -19929,7 +20503,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Galileo Progetti</t>
+          <t>Institute Perspectives</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -19939,7 +20513,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galileo Progetti</t>
+          <t>Institute Perspectives</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -19966,7 +20540,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>I am the best</t>
+          <t>ShipCon</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -19976,7 +20550,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>I am the best</t>
+          <t>ShipCon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -20003,7 +20577,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Institute Perspectives</t>
+          <t>Silifke Diyaliz</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -20013,7 +20587,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Institute Perspectives</t>
+          <t>Silifke Diyaliz</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -20040,7 +20614,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ShipCon</t>
+          <t>SPEL</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
@@ -20050,7 +20624,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ShipCon</t>
+          <t>SPEL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -20077,7 +20651,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Silifke Diyaliz</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -20087,7 +20661,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silifke Diyaliz</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -20114,7 +20688,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SPEL</t>
+          <t>Universal mobility</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -20124,7 +20698,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SPEL</t>
+          <t>Universal mobility</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20151,7 +20725,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>UX Solutions</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -20161,7 +20735,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>UX Solutions</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -20188,7 +20762,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Universal mobility</t>
+          <t>Amadeus Association</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
@@ -20198,7 +20772,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Universal mobility</t>
+          <t>Amadeus Association</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -20225,7 +20799,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UX Solutions</t>
+          <t>APDI</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -20235,7 +20809,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UX Solutions</t>
+          <t>APDI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -20262,7 +20836,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Amadeus Association</t>
+          <t>APSU</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
@@ -20272,7 +20846,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amadeus Association</t>
+          <t>APSU</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -20299,7 +20873,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>APDI</t>
+          <t>Arte Psy Association</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -20309,7 +20883,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>APDI</t>
+          <t>Arte Psy Association</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -20336,7 +20910,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>APSU</t>
+          <t>Aspire-Igen LTD</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -20346,7 +20920,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>APSU</t>
+          <t>Aspire-Igen LTD</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -20373,7 +20947,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Arte Psy Association</t>
+          <t>Aviteum</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -20383,7 +20957,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arte Psy Association</t>
+          <t>Aviteum</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -20410,7 +20984,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Aspire-Igen LTD</t>
+          <t>Cardet</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
@@ -20420,7 +20994,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aspire-Igen LTD</t>
+          <t>Cardet</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -20447,7 +21021,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Aviteum</t>
+          <t>ECTE</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -20457,7 +21031,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aviteum</t>
+          <t>ECTE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -20484,7 +21058,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cardet</t>
+          <t>Eduforma</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -20494,7 +21068,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cardet</t>
+          <t>Eduforma</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -20521,7 +21095,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ECTE</t>
+          <t>Expert Psy</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -20531,7 +21105,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ECTE</t>
+          <t>Expert Psy</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -20558,7 +21132,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Eduforma</t>
+          <t>FFE</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -20568,7 +21142,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eduforma</t>
+          <t>FFE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -20595,7 +21169,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Expert Psy</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -20605,7 +21179,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Expert Psy</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -20632,7 +21206,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FFE</t>
+          <t>Forpro Creteil</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -20642,7 +21216,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FFE</t>
+          <t>Forpro Creteil</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -20669,7 +21243,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>Fuitec</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -20679,7 +21253,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>Fuitec</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -20706,7 +21280,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Forpro Creteil</t>
+          <t>Fundatia Danis</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -20716,7 +21290,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Forpro Creteil</t>
+          <t>Fundatia Danis</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -20743,7 +21317,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fuitec</t>
+          <t>Idea</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -20753,7 +21327,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fuitec</t>
+          <t>Idea</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -20780,7 +21354,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fundatia Danis</t>
+          <t>Innogate to Europe</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -20790,7 +21364,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fundatia Danis</t>
+          <t>Innogate to Europe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -20817,7 +21391,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Innova SRL</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -20827,7 +21401,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Innova SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -20854,7 +21428,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Innogate to Europe</t>
+          <t>Innovation Frontiers</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
@@ -20864,7 +21438,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Innogate to Europe</t>
+          <t>Innovation Frontiers</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -20891,7 +21465,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Innova SRL</t>
+          <t>ITD</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -20901,7 +21475,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Innova SRL</t>
+          <t>ITD</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -20928,7 +21502,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Innovation Frontiers</t>
+          <t>Joudg "Breshia"</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
@@ -20938,7 +21512,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Innovation Frontiers</t>
+          <t>Joudg "Breshia"</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -20965,7 +21539,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ITD</t>
+          <t>Peipsi CTC</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -20975,7 +21549,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ITD</t>
+          <t>Peipsi CTC</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -21002,7 +21576,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Joudg "Breshia"</t>
+          <t>Personnel Training</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
@@ -21012,7 +21586,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Joudg "Breshia"</t>
+          <t>Personnel Training</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -21039,7 +21613,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Peipsi CTC</t>
+          <t>Prios</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -21049,7 +21623,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Peipsi CTC</t>
+          <t>Prios</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -21076,7 +21650,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Personnel Training</t>
+          <t>Proficio Skopje</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
@@ -21086,7 +21660,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Personnel Training</t>
+          <t>Proficio Skopje</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -21113,7 +21687,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Prios</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -21123,7 +21697,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Prios</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -21150,7 +21724,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Proficio Skopje</t>
+          <t>SIPOB</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
@@ -21160,7 +21734,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Proficio Skopje</t>
+          <t>SIPOB</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -21187,7 +21761,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>VekstTorget</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -21197,7 +21771,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>VekstTorget</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -21224,7 +21798,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SIPOB</t>
+          <t>Weltgewandt</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
@@ -21234,7 +21808,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SIPOB</t>
+          <t>Weltgewandt</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -21261,17 +21835,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VekstTorget</t>
+          <t>praxisnetwork.eu</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VekstTorget</t>
+          <t>http://www.praxisnetwork.eu/</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -21293,22 +21867,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>campus</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Weltgewandt</t>
+          <t>Uniwersytet WSEI w Lublinie</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Weltgewandt</t>
+          <t>ul. Projektowa 4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -21330,22 +21904,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>campus</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>praxisnetwork.eu</t>
+          <t>Filia w Warszawie</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>http://www.praxisnetwork.eu/</t>
+          <t>Filia w Warszawie</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -21357,32 +21931,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>campus</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Uniwersytet WSEI w Lublinie</t>
+          <t>Szalánczy Gábor</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ul. Projektowa 4</t>
+          <t>Szalánczy Gábor ... ERASMUS+ Koordinátor – történelem tanár</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -21394,32 +21968,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>r015</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lubelska Akademia WSEI</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>campus</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Filia w Warszawie</t>
+          <t>Papp András</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://europa2000.hu/</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Filia w Warszawie</t>
+          <t>Papp András, igazgató</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -21441,12 +22015,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Szalánczy Gábor</t>
+          <t>Muurame Lukio</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -21456,7 +22030,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Szalánczy Gábor ... ERASMUS+ Koordinátor – történelem tanár</t>
+          <t>🇫🇮 a finn Muurame Lukio képviselői</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -21478,22 +22052,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Papp András</t>
+          <t>IES Álvaro Cunqueiro</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Papp András, igazgató</t>
+          <t>🇪🇸 az IES Álvaro Cunqueiro (Vigo) képviselője</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -21520,7 +22094,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Muurame Lukio</t>
+          <t>IES Isabel de Villena</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -21530,7 +22104,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>🇫🇮 a finn Muurame Lukio képviselői</t>
+          <t>🇪🇸 az IES Isabel de Villena (Valencia) képviselője</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -21557,7 +22131,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>IES Álvaro Cunqueiro</t>
+          <t>IES El Batán</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -21567,7 +22141,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES Álvaro Cunqueiro (Vigo) képviselője</t>
+          <t>🇪🇸 az IES El Batán (Gran Canaria) diákcsoportja és kísérői</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -21594,7 +22168,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>IES Isabel de Villena</t>
+          <t>Csutak Vilmos Pedagógusok Háza</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
@@ -21604,7 +22178,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES Isabel de Villena (Valencia) képviselője</t>
+          <t>🇷🇴 a Csutak Vilmos Pedagógusok Háza pedagógusai Erdélyből</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -21631,17 +22205,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>IES El Batán</t>
+          <t>ALFMED</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES El Batán (Gran Canaria) diákcsoportja és kísérői</t>
+          <t>FRANCIAORSZÁG – PERPIGNAN – ALFMED (2018. március 19-26.)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -21668,17 +22242,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Csutak Vilmos Pedagógusok Háza</t>
+          <t>Notre Dame De Bon Secours Katolikus Magán Középiskola</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>🇷🇴 a Csutak Vilmos Pedagógusok Háza pedagógusai Erdélyből</t>
+          <t>Első utunk a Notre Dame De Bon Secours Katolikus Magán Középiskolába vezetett, amely egy patinás, 19. századi épületegyüttesben található Perpignan óvárosában. Az iskolát 1871-ben alapították, 144 éves múltra tekint vissza és jelenleg összesen 1500 diák oktatásáról és neveléséről gondoskodik középiskolai és érettségi utáni felnőtt – képzés keretében. Az iskola látogatásakor az intézmény vezetői, igazgatója és igazgató helyettese, egy angol tanár és a pályázatfelelős, illetve az intézményben tanu</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -21705,7 +22279,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ALFMED</t>
+          <t>Lycee Christian Bourquin VET School</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -21715,7 +22289,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FRANCIAORSZÁG – PERPIGNAN – ALFMED (2018. március 19-26.)</t>
+          <t>Következő látogatásunkat a dél –franciaországi régió egyik legmodernebb közép és főiskolájában – Lycee Christian Bourquin VET School – ban tettük.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -21742,7 +22316,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Notre Dame De Bon Secours Katolikus Magán Középiskola</t>
+          <t>Irish Education Partners</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -21752,7 +22326,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Első utunk a Notre Dame De Bon Secours Katolikus Magán Középiskolába vezetett, amely egy patinás, 19. századi épületegyüttesben található Perpignan óvárosában. Az iskolát 1871-ben alapították, 144 éves múltra tekint vissza és jelenleg összesen 1500 diák oktatásáról és neveléséről gondoskodik középiskolai és érettségi utáni felnőtt – képzés keretében. Az iskola látogatásakor az intézmény vezetői, igazgatója és igazgató helyettese, egy angol tanár és a pályázatfelelős, illetve az intézményben tanu</t>
+          <t>ÍRORSZÁG – DUBLIN – Irish Educaton Partners (2018. március 7-14.)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -21779,17 +22353,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Lycee Christian Bourquin VET School</t>
+          <t>Sedat Karan Anadolu Lisesi</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Következő látogatásunkat a dél –franciaországi régió egyik legmodernebb közép és főiskolájában – Lycee Christian Bourquin VET School – ban tettük.</t>
+          <t>2025 májusában lehetőségem nyílt arra, hogy Erasmus+ mobilitás keretében szakmai látogatáson (job shadowing) vegyek részt Törökországban. A Bursa kerülethez tartozó Mustafakemalpaşa település Sedat Karan Anadolu Lisesi […]</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -21816,17 +22390,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Irish Education Partners</t>
+          <t>Hannah-Arendt Gimnázium</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ÍRORSZÁG – DUBLIN – Irish Educaton Partners (2018. március 7-14.)</t>
+          <t>ERASMUS+ job-shadowing mobilitási tevékenység Egy Erasmus-programnak köszönhetően február elején egy hetet tölthettem Berlin városában, a Hannah-Arendt Gimnáziumban. Célom az volt, hogy megismerjem a német oktatási rendszer […]</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -21853,17 +22427,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sedat Karan Anadolu Lisesi</t>
+          <t>Mankolan koulu</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2025 májusában lehetőségem nyílt arra, hogy Erasmus+ mobilitás keretében szakmai látogatáson (job shadowing) vegyek részt Törökországban. A Bursa kerülethez tartozó Mustafakemalpaşa település Sedat Karan Anadolu Lisesi […]</t>
+          <t>2026. január 26. és február 1. között Erasmus+ mobilitás keretében lehetőségem nyílt szakmai job shadowing programon részt venni a finnországi Jyväskylä városában működő Mankolan koulu általános […]</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -21890,17 +22464,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Hannah-Arendt Gimnázium</t>
+          <t>Farel College</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ERASMUS+ job-shadowing mobilitási tevékenység Egy Erasmus-programnak köszönhetően február elején egy hetet tölthettem Berlin városában, a Hannah-Arendt Gimnáziumban. Célom az volt, hogy megismerjem a német oktatási rendszer […]</t>
+          <t>Helyszín: Amersfoort, Farel CollegeIdőszak: 2025.november 17-21. Amersfoorti tartózkodásom legnagyobb élménye a holland iskolai rendszerbe való betekintési lehetőség volt. A rendszer ott is sérülékeny, és sok ponton […]</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -21922,22 +22496,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>campus</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mankolan koulu</t>
+          <t>Európa 2000 Gimnázium</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
+          <t>https://europa2000.hu/</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026. január 26. és február 1. között Erasmus+ mobilitás keretében lehetőségem nyílt szakmai job shadowing programon részt venni a finnországi Jyväskylä városában működő Mankolan koulu általános […]</t>
+          <t>Európa 2000 Gimnázium - kéttannyelvű alternatív gimnázium</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -21949,12 +22523,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r031</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>ESCUELA SUPERIOR DE ARTE DRAMÁTICO DE CASTILLA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -21964,94 +22538,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Farel College</t>
+          <t>Organización de Estados Iberoamericanos (OEI)</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
+          <t>https://www.educa.jcyl.es/profesorado/en/internacionalizacion-educacion-escolar/cooperacion-portugal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Helyszín: Amersfoort, Farel CollegeIdőszak: 2025.november 17-21. Amersfoorti tartózkodásom legnagyobb élménye a holland iskolai rendszerbe való betekintési lehetőség volt. A rendszer ott is sérülékeny, és sok ponton […]</t>
+          <t>Además, la Dirección General de Innovación y Formación del Profesorado trabaja con la Organización de Estados Iberoamericanos (OEI) en la puesta en marca de actuaciones de innovación educativa en cooperación con las autoridades lusas.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>r018</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Europa 2000</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>campus</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Európa 2000 Gimnázium</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>https://europa2000.hu/</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Európa 2000 Gimnázium - kéttannyelvű alternatív gimnázium</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>r031</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>ESCUELA SUPERIOR DE ARTE DRAMÁTICO DE CASTILLA</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Organización de Estados Iberoamericanos (OEI)</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>https://www.educa.jcyl.es/profesorado/en/internacionalizacion-educacion-escolar/cooperacion-portugal</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Además, la Dirección General de Innovación y Formación del Profesorado trabaja con la Organización de Estados Iberoamericanos (OEI) en la puesta en marca de actuaciones de innovación educativa en cooperación con las autoridades lusas.</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
@@ -22181,8 +22681,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22964,7 +23462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -22994,7 +23492,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>International partners (27) - those with no country stated are last</t>
+          <t>International partners (34) - those with no country stated are last</t>
         </is>
       </c>
     </row>
@@ -23038,12 +23536,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Institut National de Recherche Biomédicale (INRB)</t>
+          <t>Instituto de Medicina Tropical “Pedro Kourí”</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23075,12 +23573,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Instituto de Medicina Tropical “Pedro Kourí”</t>
+          <t>Bernhard Nocht Institute for Tropical Medicine</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23095,7 +23593,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -23105,19 +23603,19 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bernhard Nocht Institute for Tropical Medicine (BNITM)</t>
+          <t>Ecodevelopment</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23127,7 +23625,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -23149,12 +23647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecodevelopment</t>
+          <t>Goethe University</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23164,7 +23662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -23186,7 +23684,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Goethe University</t>
+          <t>Institute of International Health Charité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -23206,7 +23704,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -23223,12 +23721,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Institute of International Health Charité</t>
+          <t>McGill Summer Institute</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -23243,7 +23741,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -23260,12 +23758,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>McGill Summer Institute</t>
+          <t>National Reference Center for Rickettsioses</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23280,7 +23778,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -23297,7 +23795,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>National Reference Center for Rickettsioses (NRCR)</t>
+          <t>Aix-Marseille University</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -23317,7 +23815,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -23334,12 +23832,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aix-Marseille University</t>
+          <t>AP Hogeschool Antwerpen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -23349,12 +23847,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>college</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -23364,14 +23862,14 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AP Hogeschool Antwerpen</t>
+          <t>Erasmushogeschool Brussel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -23408,7 +23906,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Erasmushogeschool Brussel</t>
+          <t>Antwerp Maritime Academy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -23445,7 +23943,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Antwerp Maritime Academy</t>
+          <t>HOGENT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -23482,7 +23980,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HOGENT</t>
+          <t>Howest</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -23519,7 +24017,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Howest</t>
+          <t>Arteveldehogeschool</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -23556,7 +24054,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Arteveldehogeschool</t>
+          <t>Vrije Universiteit Brussel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -23571,7 +24069,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -23593,7 +24091,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vrije Universiteit Brussel</t>
+          <t>Universiteit Antwerpen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -23630,7 +24128,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Universiteit Antwerpen</t>
+          <t>Universiteit Gent</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -23667,14 +24165,10 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Universiteit Gent</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+          <t>tropEd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>International</t>
@@ -23682,12 +24176,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -23697,19 +24191,19 @@
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fonds Wetenschappelijk Onderzoek Vlaanderen</t>
+          <t>McGill Summer Institute in Montréal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -23719,12 +24213,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -23734,7 +24228,7 @@
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
     </row>
@@ -23744,11 +24238,7 @@
           <t>Nova Academy</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>International</t>
@@ -23771,19 +24261,19 @@
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bernhard Nocht Institute for Tropical Medicine</t>
+          <t>Belgische Directoraat-Generaal voor Ontwikkelingssamenwerking en Humanitaire Hulp (DGD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -23793,12 +24283,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -23808,19 +24298,19 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tropEd</t>
+          <t>Vlaamse Regering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -23830,7 +24320,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -23845,21 +24335,17 @@
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UGent</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+          <t>Be-cause Health</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>International</t>
@@ -23867,7 +24353,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -23882,21 +24368,17 @@
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Universitair Ziekenhuis Antwerpen (UZA)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+          <t>LINQED</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>International</t>
@@ -23904,7 +24386,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -23919,29 +24401,25 @@
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl/contact</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Armauer Hansen Research Institute</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Emerging Voices for Global Health</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -23956,29 +24434,25 @@
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Africalia</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Fiabel</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -23988,114 +24462,169 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>European Society of Mycobacteriology</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>International Health Policies</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>https://www.itg.be/nl/internationale-samenwerking</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UAntwerpen</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Campuses (3)</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Bernhard Nocht Institute for Tropical Medicine (BNITM)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Campus</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Verified?</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Goethe University in Frankfurt</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hoofdgebouw</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>België</t>
-        </is>
-      </c>
+          <t>Institute of International Health Charité in Berlin</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Antwerpen</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>yes</t>
@@ -24103,71 +24632,210 @@
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ITM Campus Rochus</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
+          <t>UGent</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>branch</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>https://www.itg.be/nl</t>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ITG-DRC</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
+          <t>National Reference Center for Rickettsioses (NRCR)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Erasmushogeschool</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Campuses (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Verified?</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Instituut voor Tropische Geneeskunde</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>België</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Antwerpen</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>https://www.itg.be/nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Vestiging ITG-DRC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Democratische Republiek Congo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kinshasa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>international</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
@@ -24203,9 +24871,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_hei/batch-20261003-2347/results.xlsx
+++ b/data_hei/batch-20261003-2347/results.xlsx
@@ -704,7 +704,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
@@ -750,17 +750,17 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2 of 2 verified</t>
+          <t>10 of 10 verified</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -772,17 +772,17 @@
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>The evidence does not list any international Erasmus+ partners, only local business partners. No specific staff names or titles are provided beyond a general email address.</t>
+          <t>The evidence lists several partner institutions and organizations, but no staff names or specific contact titles are explicitly provided on the website pages.</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>site found via: web search (DuckDuckGo). mode: gemini.</t>
+          <t>site found via: remembered from an earlier run. mode: gemini.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:30Z</t>
+          <t>2026-10-22T20:05:28Z</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3600,17 +3600,17 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>0 of 1 verified</t>
+          <t>1 of 1 verified</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -3940,7 +3940,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
-    <hyperlink ref="M2" location="'r001 Sukromna spojena skola Stu'!A1" display="2"/>
+    <hyperlink ref="M2" location="'r001 Sukromna spojena skola Stu'!A1" display="10"/>
     <hyperlink ref="N2" location="'r001 Sukromna spojena skola Stu'!A1" display="2"/>
     <hyperlink ref="B5" location="'Contacts'!A2" display="Stéphanie CHAMONTIN"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
@@ -3970,7 +3970,6 @@
     <hyperlink ref="N20" location="'r023 unit'!A1" display="1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD20" r:id="rId14"/>
-    <hyperlink ref="I27" location="'Needs Review'!A123" display="yes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId15"/>
     <hyperlink ref="M27" location="'r031 ESCUELA SUPERIOR DE ARTE D'!A1" display="1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId16"/>
@@ -4857,7 +4856,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -5875,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5948,7 +5947,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DREVOREZ – Gabriel Vígh</t>
+          <t>MŠVVaŠ SR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5963,7 +5962,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5998,7 +5997,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>DREVOREZ – Gabriel Vígh</t>
+          <t>[MŠVVaŠ SR]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -6008,14 +6007,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:30Z</t>
+          <t>2026-10-22T20:05:28Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Píla Svodín</t>
+          <t>KŠÚ v Nitre</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6030,7 +6029,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6065,7 +6064,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Píla Svodín – drevorez@stonline.sk</t>
+          <t>[KŠÚ v Nitre]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -6075,3427 +6074,3427 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:30Z</t>
+          <t>2026-10-22T20:05:28Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>ASŠaŠZS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[ASŠaŠZS]</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SAMP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[SAMP]</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VŠLG Přerov</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[VŠLG Přerov]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VBC NITRA, s. r. o.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[VBC NITRA, s. r. o.]</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TURR Baja</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[TURR Baja (partnerská škola - partneriskola)]</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junior achievement sr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[junior achievement sr]</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DREVOREZ – Gabriel Vígh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[drevorez1]DREVOREZ – Gabriel Vígh</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Píla Svodín</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>r001</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sukromna spojena skola Sturovo</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Píla Svodín – drevorez@stonline.sk</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:05:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>University of Preston</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus-anglais</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>- Promote mobility at regional level through our partnership with the Nîmes Alès Metropolitan Center and the Maison de l'Europe by funding a linguistic and cultural stay for a small group of students on the UCLAN Campus, campus of the University of Preston , town twinned with the town of Nîmes;</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Malta Tourism Institute</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus-anglais</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>We are doing everything possible, notably through our partnership with the University of Nîmes for the professional license "Knowledge of Heritage" to forge links in particular with the Malta Tourism Institute.</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>UCLAN Campus</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus-anglais</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>- Promote mobility at regional level through our partnership with the Nîmes Alès Metropolitan Center and the Maison de l'Europe by funding a linguistic and cultural stay for a small group of students on the UCLAN Campus, campus of the University of Preston , town twinned with the town of Nîmes;</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Campus UCLAN</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>- Promouvoir la mobilité au niveau régional à travers notre partenariat avec le Pôle Métropolitain Nîmes Alès et la Maison de l’Europe en finançant un séjour linguistique et culturel à un petit groupe d’étudiants sur le Campus UCLAN, campus de l’Université de Preston, ville jumelée avec la ville de Nîmes ;</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Université de Preston</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>- Promouvoir la mobilité au niveau régional à travers notre partenariat avec le Pôle Métropolitain Nîmes Alès et la Maison de l’Europe en finançant un séjour linguistique et culturel à un petit groupe d’étudiants sur le Campus UCLAN, campus de l’Université de Preston, ville jumelée avec la ville de Nîmes ;</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Institut du Tourisme de Malte</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Collaborer avec des partenaires de l’enseignement supérieur est un point que nous nous efforçons de mettre en œuvre même si la reconnaissance du niveau BTS à bac+2 n’est pas homogène au sein de l’Union Européenne. Nous mettons tout en œuvre, à travers, notamment, notre partenariat avec l’Université de Nîmes pour la licence professionnelle « Connaissance du patrimoine » pour tisser des liens en particulier avec l’Institut du Tourisme de Malte.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>UCLAN, campus de la Universidad de Preston</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus-espagnol</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>- Promover la movilidad a nivel regional a través de nuestra asociación con el Centro Metropolitano Nîmes Alès y la Maison de l'Europe mediante la financiación de una estancia lingüística y cultural para un pequeño grupo de estudiantes en el campus de UCLAN, campus de la Universidad de Preston , ciudad hermanada con la ciudad de Nimes;</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Instituto de Turismo de Malta</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus-espagnol</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Colaborar con socios en la educación superior es un punto que nos esforzamos por implementar incluso si el reconocimiento del nivel BTS en bac + 2 no es homogéneo dentro de la Unión Europea. Estamos haciendo todo lo posible, especialmente a través de nuestra asociación con la Universidad de Nimes para la licencia profesional "Conocimiento del Patrimonio" para forjar vínculos en particular con el Instituto de Turismo de Malta.</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Europe Education Formation</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>34959494600
 LYCEE VINCENT DEPAUL
 escuela Joan XXIII</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>https://www.vincentdepaul30.com/strategie-erasmus-espagnol</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>• varios programas europeos con la agencia Europe Education Formation:</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2026-10-04T06:48:36Z</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Instituto de Medicina Tropical “Pedro Kourí”</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Cuba</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Yanisley Martínez López, Instituto de Medicina Tropical “Pedro Kourí” (Cuba)</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Bernhard Nocht Institute for Tropical Medicine</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>In 2024, ITM junior researcher and PhD student Johanna Bouckaert attended a training at the Bernhard Nocht Institute for Tropical Medicine (BNITM) in Hamburg, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Ecodevelopment</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>staff</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>From 6 to 17 July 2026, Stien Vereecken and Emma Vandenberghe, two ITM scientists from the Unit of Entomology, participated in a specialised training programme at Ecodevelopment in Greece, with the support of an Erasmus+ staff mobility grant.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Goethe University</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>staff</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>From 1 to 5 July 2024, PhD candidate Adwine Vanslembrouck had the opportunity to follow a field training with Goethe University in Frankfurt, supported by an Erasmus+ mobility grant</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Institute of International Health Charité</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>From 3 to 14 June 2024, ITM junior researcher and part-time MPH student Luciana Lepore followed a tropEd-accredited training on Qualitative Research Methods and Data Management at the Institute of International Health Charité in Berlin, supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>McGill Summer Institute</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>National Reference Center for Rickettsioses</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
+      <c r="J27" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>From 4 to 15 March 2024, ITM PhD student Carl Boodman participated in a training programme at the National Reference Center for Rickettsioses (NRCR) in Marseille, France, affiliated with Aix-Marseille University. His participation was supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Aix-Marseille University</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>From 4 to 15 March 2024, ITM PhD student Carl Boodman participated in a training programme at the National Reference Center for Rickettsioses (NRCR) in Marseille, France, affiliated with Aix-Marseille University. His participation was supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>AP Hogeschool Antwerpen</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Erasmushogeschool Brussel</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Antwerp Maritime Academy</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>HOGENT</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Howest</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Arteveldehogeschool</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
+      <c r="J34" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Vrije Universiteit Brussel</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Universiteit Antwerpen</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Universiteit Gent</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>De tien partners in Nova Academy zijn AP Hogeschool Antwerpen, Erasmushogeschool Brussel, het Instituut voor Tropische Geneeskunde, Antwerp Maritime Academy, HOGENT, Howest, Arteveldehogeschool, Vrije Universiteit Brussel, Universiteit Antwerpen en de Universiteit Gent. De officiële lancering vond plaats op vrijdag 29 mei aan de Erasmushogeschool in Brussel, in aanwezigheid van de rectoren en directeuren van de betrokken instellingen.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>tropEd</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Do you want to follow a (blended) course at one of the tropEd partner institutions? Or would you like to do a traineeship at one of ITM’s international partner institutions to strengthen your lab skills or to collect field data for your thesis?</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>McGill Summer Institute in Montréal</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Nova Academy</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Op vrijdag 29 mei 2026 vond de officiële lancering van de vernieuwde Nova Academy plaats aan de Erasmushogeschool in Brussel. Wat in 2021 begon als een samenwerking tussen drie universiteiten, is uitgegroeid tot een sterk partnerschap van tien Vlaamse instellingen voor hoger onderwijs die samen inzetten op levenslang leren. Ook het Instituut voor Tropische Geneeskunde (ITG) maakt deel uit van de samenwerking. Algemeen beheerder Ann Peters vertegenwoordigde het ITG tijdens dit feestelijke eveneme</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Belgische Directoraat-Generaal voor Ontwikkelingssamenwerking en Humanitaire Hulp (DGD)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Het ITG werkt samen met 24 partners, verspreid over drie continenten. De partnerschappen worden gefinancierd met een vijfjarensubsidie van het Belgische Directoraat-Generaal voor Ontwikkelingssamenwerking en Humanitaire Hulp (DGD). De Vlaamse Regering financiert daarnaast nog twee partnerschappen in Mozambique.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Vlaamse Regering</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Het ITG werkt samen met 24 partners, verspreid over drie continenten. De partnerschappen worden gefinancierd met een vijfjarensubsidie van het Belgische Directoraat-Generaal voor Ontwikkelingssamenwerking en Humanitaire Hulp (DGD). De Vlaamse Regering financiert daarnaast nog twee partnerschappen in Mozambique.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Be-cause Health</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J35" s="1" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Be-cause Health</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>LINQED</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J36" s="1" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>LINQED</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Emerging Voices for Global Health</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Emerging Voices for Global Health</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Fiabel</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="J46" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Fiabel</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>International Health Policies</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/internationale-samenwerking</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>International Health Policies</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>UAntwerpen</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>UAntwerpen (TBD)</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Bernhard Nocht Institute for Tropical Medicine (BNITM)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>staff</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J41" s="1" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>In 2024, ITM junior researcher and PhD student Johanna Bouckaert attended a training at the Bernhard Nocht Institute for Tropical Medicine (BNITM) in Hamburg, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Goethe University in Frankfurt</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J42" s="1" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>From 1 to 5 July 2024, PhD candidate Adwine Vanslembrouck had the opportunity to follow a field training with Goethe University in Frankfurt, supported by an Erasmus+ mobility grant</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Institute of International Health Charité in Berlin</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J43" s="1" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>From 3 to 14 June 2024, ITM junior researcher and part-time MPH student Luciana Lepore followed a tropEd-accredited training on Qualitative Research Methods and Data Management at the Institute of International Health Charité in Berlin, supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>UGent</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>From 3 to 7 June 2024, PhD student Jens Cornelis (at ITM and UGent) attended a training on Global Health Diagnostics at the McGill Summer Institute in Montréal, Canada, with the support of an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>National Reference Center for Rickettsioses (NRCR)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J45" s="1" t="inlineStr">
+      <c r="J53" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/en/study/mobility#erasmus-plus</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>From 4 to 15 March 2024, ITM PhD student Carl Boodman participated in a training programme at the National Reference Center for Rickettsioses (NRCR) in Marseille, France, affiliated with Aix-Marseille University. His participation was supported by an Erasmus+ mobility grant.</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Erasmushogeschool</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>college</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>r007</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>PRINS LEOPOLD INSTITUUT VOOR TROPISCHE GENEESKUND
 Escuela Superior de Arte Dramático de Valencia</t>
         </is>
       </c>
-      <c r="J46" s="1" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
         <is>
           <t>https://www.itg.be/nl/health-stories/artikels/nieuw-partnerschap-versterkt-levenslang-leren-in-Vlaanderen</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Op vrijdag 29 mei 2026 vond de officiële lancering van de vernieuwde Nova Academy plaats aan de Erasmushogeschool in Brussel. Wat in 2021 begon als een samenwerking tussen drie universiteiten, is uitgegroeid tot een sterk partnerschap van tien Vlaamse instellingen voor hoger onderwijs die samen inzetten op levenslang leren. Ook het Instituut voor Tropische Geneeskunde (ITG) maakt deel uit van de samenwerking. Algemeen beheerder Ann Peters vertegenwoordigde het ITG tijdens dit feestelijke eveneme</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>2026-10-22T12:27:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>PNTTE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>praxisnetwork.eu</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>http://www.praxisnetwork.eu/</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Batman Universitesi</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Country not stated</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Batman Universitesi</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>COFAC</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Country not stated</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>COFAC</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>CULS Prague</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Country not stated</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>CULS Prague</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ETEA</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Country not stated</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>ETEA</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Fachhochschule des Mittelstandes</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Country not stated</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Fachhochschule des Mittelstandes</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>HEL</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Country not stated</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>r015</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Lubelska Akademia WSEI</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>HEL</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IPB</t>
+          <t>PNTTE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9505,12 +9504,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9540,12 +9539,12 @@
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>IPB</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -9562,7 +9561,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kirklareli University</t>
+          <t>praxisnetwork.eu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9572,12 +9571,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9607,12 +9606,12 @@
       </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/dla-studenta/erasmus/</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Kirklareli University</t>
+          <t>http://www.praxisnetwork.eu/</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -9629,7 +9628,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Loyola University</t>
+          <t>Batman Universitesi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9679,7 +9678,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Loyola University</t>
+          <t>Batman Universitesi</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -9696,7 +9695,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
+          <t>COFAC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9746,7 +9745,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
+          <t>COFAC</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -9763,7 +9762,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Paderborn University</t>
+          <t>CULS Prague</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9813,7 +9812,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Paderborn University</t>
+          <t>CULS Prague</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -9830,7 +9829,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Panepistimio Thessalias</t>
+          <t>ETEA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9880,7 +9879,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Panepistimio Thessalias</t>
+          <t>ETEA</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9897,7 +9896,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PEGASO</t>
+          <t>Fachhochschule des Mittelstandes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9947,7 +9946,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>PEGASO</t>
+          <t>Fachhochschule des Mittelstandes</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9964,7 +9963,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sia Biznesa Augstskola Turiba</t>
+          <t>HEL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10014,7 +10013,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Sia Biznesa Augstskola Turiba</t>
+          <t>HEL</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -10031,7 +10030,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SMK Aukštoji Mokykla</t>
+          <t>IPB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10081,7 +10080,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>SMK Aukštoji Mokykla</t>
+          <t>IPB</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -10098,7 +10097,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TSI</t>
+          <t>Kirklareli University</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10148,7 +10147,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>TSI</t>
+          <t>Kirklareli University</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -10165,7 +10164,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UFUK University</t>
+          <t>Loyola University</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10215,7 +10214,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>UFUK University</t>
+          <t>Loyola University</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -10232,7 +10231,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Universidad de Alicante</t>
+          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10282,7 +10281,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Universidad de Alicante</t>
+          <t>Maieutica Cooperativa de Ensino Superior CRL</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -10299,7 +10298,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Universidad de la Laguna</t>
+          <t>Paderborn University</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10349,7 +10348,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Universidad de la Laguna</t>
+          <t>Paderborn University</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -10366,7 +10365,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>University of Žilina</t>
+          <t>Panepistimio Thessalias</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10416,7 +10415,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>University of Žilina</t>
+          <t>Panepistimio Thessalias</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -10433,7 +10432,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Univerza v Mariboru</t>
+          <t>PEGASO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10483,7 +10482,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Univerza v Mariboru</t>
+          <t>PEGASO</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -10500,7 +10499,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Veleučilište Aspira</t>
+          <t>Sia Biznesa Augstskola Turiba</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -10550,7 +10549,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Veleučilište Aspira</t>
+          <t>Sia Biznesa Augstskola Turiba</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -10567,7 +10566,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WU Wien</t>
+          <t>SMK Aukštoji Mokykla</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10617,7 +10616,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>WU Wien</t>
+          <t>SMK Aukštoji Mokykla</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -10634,7 +10633,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Uniwersytet Stanforda</t>
+          <t>TSI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10679,12 +10678,12 @@
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Dyrektor Instytutu Informatyki i Innowacyjnych technologii. Zaklasyfikowany jako top2% najbardziej wpływowych ludzie w świecie nauki przez Uniwersytet Stanforda</t>
+          <t>TSI</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -10701,7 +10700,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PKN Orlen</t>
+          <t>UFUK University</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10716,7 +10715,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -10746,12 +10745,12 @@
       </c>
       <c r="J73" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>UFUK University</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -10768,7 +10767,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KGHM</t>
+          <t>Universidad de Alicante</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10783,7 +10782,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -10813,12 +10812,12 @@
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>Universidad de Alicante</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -10835,7 +10834,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Grupa Azoty</t>
+          <t>Universidad de la Laguna</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10850,7 +10849,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -10880,12 +10879,12 @@
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
+          <t>Universidad de la Laguna</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -10902,7 +10901,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PKS Ryki</t>
+          <t>University of Žilina</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10917,7 +10916,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -10947,12 +10946,12 @@
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
+          <t>University of Žilina</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -10969,7 +10968,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cewar Lublin</t>
+          <t>Univerza v Mariboru</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10984,7 +10983,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11014,12 +11013,12 @@
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
+          <t>Univerza v Mariboru</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -11036,7 +11035,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AIE</t>
+          <t>Veleučilište Aspira</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -11051,7 +11050,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -11086,7 +11085,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>AIE</t>
+          <t>Veleučilište Aspira</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -11103,7 +11102,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ashina Records</t>
+          <t>WU Wien</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -11118,7 +11117,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -11153,7 +11152,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ashina Records</t>
+          <t>WU Wien</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -11170,7 +11169,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Axel Lugo</t>
+          <t>Uniwersytet Stanforda</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -11185,7 +11184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -11215,12 +11214,12 @@
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Axel Lugo</t>
+          <t>Dyrektor Instytutu Informatyki i Innowacyjnych technologii. Zaklasyfikowany jako top2% najbardziej wpływowych ludzie w świecie nauki przez Uniwersytet Stanforda</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -11237,7 +11236,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BBCA</t>
+          <t>PKN Orlen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -11252,7 +11251,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -11282,12 +11281,12 @@
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>BBCA</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -11304,7 +11303,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Capture Models</t>
+          <t>KGHM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -11349,12 +11348,12 @@
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Capture Models</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -11371,7 +11370,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EELI</t>
+          <t>Grupa Azoty</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -11386,7 +11385,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -11416,12 +11415,12 @@
       </c>
       <c r="J83" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>EELI</t>
+          <t>Ekspert w zakresie finansów i zarządzania finansami. Jako doradca współpracował z: PKN Orlen, KGHM i spółkami z Grupy Azoty</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -11438,7 +11437,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>PKS Ryki</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -11453,7 +11452,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -11483,12 +11482,12 @@
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -11505,7 +11504,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EureCons</t>
+          <t>Cewar Lublin</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -11550,12 +11549,12 @@
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
-          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
+          <t>https://www.wsei.pl/</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>EureCons</t>
+          <t>Specjalista m.in. w zakresie logistycznego zarządzania przedsiębiorstwem. Doradca Zarządów ds. restrukturyzacji procesów logistycznych w PKS Ryki oraz Cewar Lublin, członek PNTTE</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -11572,7 +11571,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FOLA nature</t>
+          <t>AIE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -11622,7 +11621,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>FOLA nature</t>
+          <t>AIE</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -11639,7 +11638,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Franziskus Spital</t>
+          <t>Ashina Records</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -11654,7 +11653,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -11689,7 +11688,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Franziskus Spital</t>
+          <t>Ashina Records</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -11706,7 +11705,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Galileo Progetti</t>
+          <t>Axel Lugo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -11756,7 +11755,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Galileo Progetti</t>
+          <t>Axel Lugo</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -11773,7 +11772,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>I am the best</t>
+          <t>BBCA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -11823,7 +11822,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>I am the best</t>
+          <t>BBCA</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -11840,7 +11839,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Institute Perspectives</t>
+          <t>Capture Models</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11855,7 +11854,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -11890,7 +11889,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Institute Perspectives</t>
+          <t>Capture Models</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -11907,7 +11906,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ShipCon</t>
+          <t>EELI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11922,7 +11921,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -11957,7 +11956,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ShipCon</t>
+          <t>EELI</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -11974,7 +11973,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Silifke Diyaliz</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -12024,7 +12023,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Silifke Diyaliz</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -12041,7 +12040,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SPEL</t>
+          <t>EureCons</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -12056,7 +12055,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12091,7 +12090,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>SPEL</t>
+          <t>EureCons</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -12108,7 +12107,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>FOLA nature</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -12158,7 +12157,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>FOLA nature</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -12175,7 +12174,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Universal mobility</t>
+          <t>Franziskus Spital</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -12225,7 +12224,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Universal mobility</t>
+          <t>Franziskus Spital</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -12242,7 +12241,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UX Solutions</t>
+          <t>Galileo Progetti</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -12257,7 +12256,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12292,7 +12291,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>UX Solutions</t>
+          <t>Galileo Progetti</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -12309,7 +12308,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Amadeus Association</t>
+          <t>I am the best</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -12359,7 +12358,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Amadeus Association</t>
+          <t>I am the best</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -12376,7 +12375,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>APDI</t>
+          <t>Institute Perspectives</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -12426,7 +12425,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>APDI</t>
+          <t>Institute Perspectives</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -12443,7 +12442,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>APSU</t>
+          <t>ShipCon</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -12458,7 +12457,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -12493,7 +12492,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>APSU</t>
+          <t>ShipCon</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -12510,7 +12509,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Arte Psy Association</t>
+          <t>Silifke Diyaliz</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -12560,7 +12559,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Arte Psy Association</t>
+          <t>Silifke Diyaliz</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -12577,7 +12576,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Aspire-Igen LTD</t>
+          <t>SPEL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -12592,7 +12591,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -12627,7 +12626,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Aspire-Igen LTD</t>
+          <t>SPEL</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -12644,7 +12643,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Aviteum</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -12694,7 +12693,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Aviteum</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -12711,7 +12710,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cardet</t>
+          <t>Universal mobility</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12761,7 +12760,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Cardet</t>
+          <t>Universal mobility</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -12778,7 +12777,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ECTE</t>
+          <t>UX Solutions</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12793,7 +12792,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12828,7 +12827,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>ECTE</t>
+          <t>UX Solutions</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -12845,7 +12844,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Eduforma</t>
+          <t>Amadeus Association</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12895,7 +12894,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Eduforma</t>
+          <t>Amadeus Association</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -12912,7 +12911,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Expert Psy</t>
+          <t>APDI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12962,7 +12961,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Expert Psy</t>
+          <t>APDI</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -12979,7 +12978,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FFE</t>
+          <t>APSU</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -13029,7 +13028,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>FFE</t>
+          <t>APSU</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -13046,7 +13045,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>Arte Psy Association</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -13096,7 +13095,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>Arte Psy Association</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -13113,7 +13112,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Forpro Creteil</t>
+          <t>Aspire-Igen LTD</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -13128,7 +13127,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -13163,7 +13162,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Forpro Creteil</t>
+          <t>Aspire-Igen LTD</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -13180,7 +13179,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Fuitec</t>
+          <t>Aviteum</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -13230,7 +13229,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Fuitec</t>
+          <t>Aviteum</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -13247,7 +13246,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Fundatia Danis</t>
+          <t>Cardet</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -13297,7 +13296,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Fundatia Danis</t>
+          <t>Cardet</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -13314,7 +13313,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>ECTE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13364,7 +13363,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>ECTE</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -13381,7 +13380,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Innogate to Europe</t>
+          <t>Eduforma</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13431,7 +13430,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Innogate to Europe</t>
+          <t>Eduforma</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -13448,7 +13447,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Innova SRL</t>
+          <t>Expert Psy</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -13463,7 +13462,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13498,7 +13497,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Innova SRL</t>
+          <t>Expert Psy</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -13515,7 +13514,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Innovation Frontiers</t>
+          <t>FFE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13565,7 +13564,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Innovation Frontiers</t>
+          <t>FFE</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -13582,7 +13581,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ITD</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13632,7 +13631,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>ITD</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -13649,7 +13648,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Joudg "Breshia"</t>
+          <t>Forpro Creteil</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13699,7 +13698,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Joudg "Breshia"</t>
+          <t>Forpro Creteil</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -13716,7 +13715,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Peipsi CTC</t>
+          <t>Fuitec</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13766,7 +13765,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Peipsi CTC</t>
+          <t>Fuitec</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -13783,7 +13782,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Personnel Training</t>
+          <t>Fundatia Danis</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13833,7 +13832,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Personnel Training</t>
+          <t>Fundatia Danis</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -13850,7 +13849,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Prios</t>
+          <t>Idea</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13900,7 +13899,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Prios</t>
+          <t>Idea</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -13917,7 +13916,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Proficio Skopje</t>
+          <t>Innogate to Europe</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13967,7 +13966,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Proficio Skopje</t>
+          <t>Innogate to Europe</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -13984,7 +13983,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Innova SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13999,7 +13998,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -14034,7 +14033,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Innova SRL</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -14051,7 +14050,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SIPOB</t>
+          <t>Innovation Frontiers</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -14101,7 +14100,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>SIPOB</t>
+          <t>Innovation Frontiers</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -14118,7 +14117,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VekstTorget</t>
+          <t>ITD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -14168,7 +14167,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>VekstTorget</t>
+          <t>ITD</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -14185,7 +14184,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Weltgewandt</t>
+          <t>Joudg "Breshia"</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -14235,7 +14234,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Weltgewandt</t>
+          <t>Joudg "Breshia"</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -14252,12 +14251,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Muurame Lukio</t>
+          <t>Peipsi CTC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14267,7 +14266,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -14287,22 +14286,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J126" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>🇫🇮 a finn Muurame Lukio képviselői</t>
+          <t>Peipsi CTC</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -14312,19 +14311,19 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IES Álvaro Cunqueiro</t>
+          <t>Personnel Training</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14334,7 +14333,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -14354,22 +14353,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J127" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES Álvaro Cunqueiro (Vigo) képviselője</t>
+          <t>Personnel Training</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -14379,19 +14378,19 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>IES Isabel de Villena</t>
+          <t>Prios</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14401,7 +14400,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -14421,22 +14420,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J128" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES Isabel de Villena (Valencia) képviselője</t>
+          <t>Prios</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -14446,19 +14445,19 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>IES El Batán</t>
+          <t>Proficio Skopje</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14468,12 +14467,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14488,22 +14487,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J129" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>🇪🇸 az IES El Batán (Gran Canaria) diákcsoportja és kísérői</t>
+          <t>Proficio Skopje</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -14513,19 +14512,19 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Csutak Vilmos Pedagógusok Háza</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14555,22 +14554,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J130" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>🇷🇴 a Csutak Vilmos Pedagógusok Háza pedagógusai Erdélyből</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -14580,19 +14579,19 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ALFMED</t>
+          <t>SIPOB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14602,12 +14601,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14622,22 +14621,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J131" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>FRANCIAORSZÁG – PERPIGNAN – ALFMED (2018. március 19-26.)</t>
+          <t>SIPOB</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -14647,19 +14646,19 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Notre Dame De Bon Secours Katolikus Magán Középiskola</t>
+          <t>VekstTorget</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14669,7 +14668,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -14689,22 +14688,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J132" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Első utunk a Notre Dame De Bon Secours Katolikus Magán Középiskolába vezetett, amely egy patinás, 19. századi épületegyüttesben található Perpignan óvárosában. Az iskolát 1871-ben alapították, 144 éves múltra tekint vissza és jelenleg összesen 1500 diák oktatásáról és neveléséről gondoskodik középiskolai és érettségi utáni felnőtt – képzés keretében. Az iskola látogatásakor az intézmény vezetői, igazgatója és igazgató helyettese, egy angol tanár és a pályázatfelelős, illetve az intézményben tanu</t>
+          <t>VekstTorget</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -14714,19 +14713,19 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Lycee Christian Bourquin VET School</t>
+          <t>Weltgewandt</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -14736,7 +14735,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -14756,22 +14755,22 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>r018</t>
+          <t>r015</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Europa 2000</t>
+          <t>Lubelska Akademia WSEI</t>
         </is>
       </c>
       <c r="J133" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://www.wsei.pl/international-cooperation/partners/#academic-cooperation</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Következő látogatásunkat a dél –franciaországi régió egyik legmodernebb közép és főiskolájában – Lycee Christian Bourquin VET School – ban tettük.</t>
+          <t>Weltgewandt</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -14781,19 +14780,19 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:01Z</t>
+          <t>2026-10-04T06:48:54Z</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Irish Education Partners</t>
+          <t>Muurame Lukio</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14803,12 +14802,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14833,12 +14832,12 @@
       </c>
       <c r="J134" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>ÍRORSZÁG – DUBLIN – Irish Educaton Partners (2018. március 7-14.)</t>
+          <t>🇫🇮 a finn Muurame Lukio képviselői</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -14855,12 +14854,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sedat Karan Anadolu Lisesi</t>
+          <t>IES Álvaro Cunqueiro</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -14875,7 +14874,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -14900,12 +14899,12 @@
       </c>
       <c r="J135" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2025 májusában lehetőségem nyílt arra, hogy Erasmus+ mobilitás keretében szakmai látogatáson (job shadowing) vegyek részt Törökországban. A Bursa kerülethez tartozó Mustafakemalpaşa település Sedat Karan Anadolu Lisesi […]</t>
+          <t>🇪🇸 az IES Álvaro Cunqueiro (Vigo) képviselője</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -14922,12 +14921,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Hannah-Arendt Gimnázium</t>
+          <t>IES Isabel de Villena</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -14942,7 +14941,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14967,12 +14966,12 @@
       </c>
       <c r="J136" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>ERASMUS+ job-shadowing mobilitási tevékenység Egy Erasmus-programnak köszönhetően február elején egy hetet tölthettem Berlin városában, a Hannah-Arendt Gimnáziumban. Célom az volt, hogy megismerjem a német oktatási rendszer […]</t>
+          <t>🇪🇸 az IES Isabel de Villena (Valencia) képviselője</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -14989,12 +14988,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mankolan koulu</t>
+          <t>IES El Batán</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15009,7 +15008,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -15034,12 +15033,12 @@
       </c>
       <c r="J137" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026. január 26. és február 1. között Erasmus+ mobilitás keretében lehetőségem nyílt szakmai job shadowing programon részt venni a finnországi Jyväskylä városában működő Mankolan koulu általános […]</t>
+          <t>🇪🇸 az IES El Batán (Gran Canaria) diákcsoportja és kísérői</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -15056,12 +15055,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Farel College</t>
+          <t>Csutak Vilmos Pedagógusok Háza</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15071,12 +15070,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -15101,12 +15100,12 @@
       </c>
       <c r="J138" s="1" t="inlineStr">
         <is>
-          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
+          <t>https://europa2000.hu/erasmus-mobilitasi-het-az-europa-2000-gimnaziumban/</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Helyszín: Amersfoort, Farel CollegeIdőszak: 2025.november 17-21. Amersfoorti tartózkodásom legnagyobb élménye a holland iskolai rendszerbe való betekintési lehetőség volt. A rendszer ott is sérülékeny, és sok ponton […]</t>
+          <t>🇷🇴 a Csutak Vilmos Pedagógusok Háza pedagógusai Erdélyből</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -15123,12 +15122,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Organización de Estados Iberoamericanos (OEI)</t>
+          <t>ALFMED</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15138,12 +15137,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15158,22 +15157,22 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>r031</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ESCUELA SUPERIOR DE ARTE DRAMÁTICO DE CASTILLA</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J139" s="1" t="inlineStr">
         <is>
-          <t>https://www.educa.jcyl.es/profesorado/en/internacionalizacion-educacion-escolar/cooperacion-portugal</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Además, la Dirección General de Innovación y Formación del Profesorado trabaja con la Organización de Estados Iberoamericanos (OEI) en la puesta en marca de actuaciones de innovación educativa en cooperación con las autoridades lusas.</t>
+          <t>FRANCIAORSZÁG – PERPIGNAN – ALFMED (2018. március 19-26.)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -15183,14 +15182,14 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-10-04T06:59:23Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Académie des César</t>
+          <t>Notre Dame De Bon Secours Katolikus Magán Középiskola</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -15205,7 +15204,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -15220,44 +15219,44 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J140" s="1" t="inlineStr">
         <is>
-          <t>https://ad-education.com/academie-des-cesar-lecv-partenaire-des-nuits-en-or/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Académie des César – L’ECV, partenaire des Nuits en Or</t>
+          <t>Első utunk a Notre Dame De Bon Secours Katolikus Magán Középiskolába vezetett, amely egy patinás, 19. századi épületegyüttesben található Perpignan óvárosában. Az iskolát 1871-ben alapították, 144 éves múltra tekint vissza és jelenleg összesen 1500 diák oktatásáról és neveléséről gondoskodik középiskolai és érettségi utáni felnőtt – képzés keretében. Az iskola látogatásakor az intézmény vezetői, igazgatója és igazgató helyettese, egy angol tanár és a pályázatfelelős, illetve az intézményben tanu</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Maddy Keynote</t>
+          <t>Lycee Christian Bourquin VET School</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -15272,7 +15271,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -15287,49 +15286,49 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J141" s="1" t="inlineStr">
         <is>
-          <t>https://ad-education.com/ecv-partenaire-la-edition-la-maddy-keynote-mkn23/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>L’ECV, partenaire de la 7e édition de la Maddy Keynote – MKN23 !</t>
+          <t>Következő látogatásunkat a dél –franciaországi régió egyik legmodernebb közép és főiskolájában – Lycee Christian Bourquin VET School – ban tettük.</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EDC</t>
+          <t>Irish Education Partners</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -15339,12 +15338,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -15354,49 +15353,49 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J142" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/megujit-bovit-fejleszt-erasmus-palyazat-munkatarsi-mobilitasok-szakmai-beszamoloja/</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>EDC</t>
+          <t>ÍRORSZÁG – DUBLIN – Irish Educaton Partners (2018. március 7-14.)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ECV</t>
+          <t>Sedat Karan Anadolu Lisesi</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -15411,7 +15410,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -15421,49 +15420,49 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J143" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>ECV</t>
+          <t>2025 májusában lehetőségem nyílt arra, hogy Erasmus+ mobilitás keretében szakmai látogatáson (job shadowing) vegyek részt Törökországban. A Bursa kerülethez tartozó Mustafakemalpaşa település Sedat Karan Anadolu Lisesi […]</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>IAAD</t>
+          <t>Hannah-Arendt Gimnázium</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -15478,7 +15477,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -15488,49 +15487,49 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J144" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/2024-1-hu01-ka121-sch-000230784-akkreditacio-2024-2025/</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>IAAD</t>
+          <t>ERASMUS+ job-shadowing mobilitási tevékenység Egy Erasmus-programnak köszönhetően február elején egy hetet tölthettem Berlin városában, a Hannah-Arendt Gimnáziumban. Célom az volt, hogy megismerjem a német oktatási rendszer […]</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Accademia Italiana</t>
+          <t>Mankolan koulu</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -15545,7 +15544,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -15555,49 +15554,49 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J145" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Accademia Italiana</t>
+          <t>2026. január 26. és február 1. között Erasmus+ mobilitás keretében lehetőségem nyílt szakmai job shadowing programon részt venni a finnországi Jyväskylä városában működő Mankolan koulu általános […]</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CEV</t>
+          <t>Farel College</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -15612,7 +15611,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -15622,44 +15621,44 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r018</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>Europa 2000</t>
         </is>
       </c>
       <c r="J146" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://europa2000.hu/palyazatok/erasmus-mobilitasi-akkreditacio/akkreditacio-2025-2026/</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>CEV</t>
+          <t>Helyszín: Amersfoort, Farel CollegeIdőszak: 2025.november 17-21. Amersfoorti tartózkodásom legnagyobb élménye a holland iskolai rendszerbe való betekintési lehetőség volt. A rendszer ott is sérülékeny, és sok ponton […]</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:49:01Z</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CES</t>
+          <t>Organización de Estados Iberoamericanos (OEI)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15674,7 +15673,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15694,44 +15693,44 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>r032</t>
+          <t>r031</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>GROUPE EAC - ING</t>
+          <t>ESCUELA SUPERIOR DE ARTE DRAMÁTICO DE CASTILLA</t>
         </is>
       </c>
       <c r="J147" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://www.educa.jcyl.es/profesorado/en/internacionalizacion-educacion-escolar/cooperacion-portugal</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>CES</t>
+          <t>Además, la Dirección General de Innovación y Formación del Profesorado trabaja con la Organización de Estados Iberoamericanos (OEI) en la puesta en marca de actuaciones de innovación educativa en cooperación con las autoridades lusas.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:01Z</t>
+          <t>2026-10-04T06:59:23Z</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Barreira Arte y Diseño</t>
+          <t>Académie des César</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -15741,7 +15740,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15771,12 +15770,12 @@
       </c>
       <c r="J148" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://ad-education.com/academie-des-cesar-lecv-partenaire-des-nuits-en-or/</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Barreira Arte y Diseño</t>
+          <t>Académie des César – L’ECV, partenaire des Nuits en Or</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -15793,12 +15792,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Media University</t>
+          <t>Maddy Keynote</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -15808,7 +15807,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15838,12 +15837,12 @@
       </c>
       <c r="J149" s="1" t="inlineStr">
         <is>
-          <t>https://en.ad-education.com/</t>
+          <t>https://ad-education.com/ecv-partenaire-la-edition-la-maddy-keynote-mkn23/</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Media University</t>
+          <t>L’ECV, partenaire de la 7e édition de la Maddy Keynote – MKN23 !</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -15860,7 +15859,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EAC</t>
+          <t>EDC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -15910,7 +15909,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>EAC</t>
+          <t>EDC</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -15927,7 +15926,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>École Supérieure du Parfum</t>
+          <t>ECV</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -15977,7 +15976,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>École Supérieure du Parfum</t>
+          <t>ECV</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -15994,7 +15993,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>IAAD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -16044,7 +16043,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>IAAD</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -16061,7 +16060,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ESD</t>
+          <t>Accademia Italiana</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -16111,7 +16110,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>ESD</t>
+          <t>Accademia Italiana</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -16128,7 +16127,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IIM</t>
+          <t>CEV</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -16178,7 +16177,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>IIM</t>
+          <t>CEV</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -16195,7 +16194,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EMLV</t>
+          <t>CES</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -16245,7 +16244,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>EMLV</t>
+          <t>CES</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -16262,7 +16261,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ESILV</t>
+          <t>Barreira Arte y Diseño</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -16312,7 +16311,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>ESILV</t>
+          <t>Barreira Arte y Diseño</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -16329,22 +16328,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ALMA</t>
+          <t>Media University</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -16364,93 +16363,629 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>r033</t>
+          <t>r032</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>UNIVERSITE GRENOBLE ALPES</t>
+          <t>GROUPE EAC - ING</t>
         </is>
       </c>
       <c r="J157" s="1" t="inlineStr">
         <is>
-          <t>https://www.univ-grenoble-alpes.fr/</t>
+          <t>https://en.ad-education.com/</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Un programme international majeur d’observations de très jeunes étoiles, dans lequel sont impliqués des scientifiques de l’Institut de planétologie et d'astrophysique de Grenoble, livre ses premiers résultats. Grâce aux observations du réseau de radiotélescopes ALMA au Chili, l’équipe scientifique a détecté des molécules et leurs traces là où elles étaient supposément rares, voire inexistantes.</t>
+          <t>Media University</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:16Z</t>
+          <t>2026-10-22T10:32:01Z</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>EAC</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J158" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>EAC</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>École Supérieure du Parfum</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J159" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>École Supérieure du Parfum</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J160" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ESD</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J161" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>ESD</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>IIM</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>IIM</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>EMLV</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J163" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>EMLV</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ESILV</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>r032</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>GROUPE EAC - ING</t>
+        </is>
+      </c>
+      <c r="J164" s="1" t="inlineStr">
+        <is>
+          <t>https://en.ad-education.com/</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>ESILV</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ALMA</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>r033</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>UNIVERSITE GRENOBLE ALPES</t>
+        </is>
+      </c>
+      <c r="J165" s="1" t="inlineStr">
+        <is>
+          <t>https://www.univ-grenoble-alpes.fr/</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Un programme international majeur d’observations de très jeunes étoiles, dans lequel sont impliqués des scientifiques de l’Institut de planétologie et d'astrophysique de Grenoble, livre ses premiers résultats. Grâce aux observations du réseau de radiotélescopes ALMA au Chili, l’équipe scientifique a détecté des molécules et leurs traces là où elles étaient supposément rares, voire inexistantes.</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>Mobicoop</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr">
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>r033</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>UNIVERSITE GRENOBLE ALPES</t>
         </is>
       </c>
-      <c r="J158" s="1" t="inlineStr">
+      <c r="J166" s="1" t="inlineStr">
         <is>
           <t>https://www.univ-grenoble-alpes.fr/stand-sur-la-transformation-ecologique-et-la-mobilite-valence-1808967.kjsp?RH=1769439721486</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="K166" t="inlineStr">
         <is>
           <t>Ce stand est aussi l'occasion de s'informer sur le lancement de "Covoit'UGA" en partenariat avec Mobicoop. Covoit'UGA est un espace de réservation de covoiturage dédié aux personnels et étudiants à l'Université Grenoble Alpes pour favoriser le covoiturage entre Grenoble et Valence. Un cours à donner ou à suivre ? Voyager en groupe !</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t>quote found on page</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t>2026-10-22T10:32:16Z</t>
         </is>
@@ -16615,6 +17150,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId165"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16724,7 +17267,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ADRESA / CÍM: Súkromná spojená škola Elokované pracovisko SSŠ – o. z. Súkromná obchodná akadémia</t>
+          <t>943 01 Štúrovo 949 01 Nitra</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -16739,7 +17282,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:30Z</t>
+          <t>2026-10-22T20:05:28Z</t>
         </is>
       </c>
     </row>
@@ -16756,7 +17299,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Elokované pracovisko SSŠ</t>
+          <t>Elokované pracovisko SSŠ – o. z. Súkromná obchodná akadémia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16781,7 +17324,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ADRESA / CÍM: Súkromná spojená škola Elokované pracovisko SSŠ – o. z. Súkromná obchodná akadémia</t>
+          <t>943 01 Štúrovo 949 01 Nitra</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -16796,7 +17339,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-04T06:49:30Z</t>
+          <t>2026-10-22T20:05:28Z</t>
         </is>
       </c>
     </row>
@@ -16908,7 +17451,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -16966,7 +17509,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -17528,7 +18071,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -17588,7 +18131,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -17648,7 +18191,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -17957,7 +18500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22515,43 +23058,6 @@
         </is>
       </c>
       <c r="G122" t="inlineStr">
-        <is>
-          <t>cited page was not read by the fetcher (cannot check)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>r031</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>ESCUELA SUPERIOR DE ARTE DRAMÁTICO DE CASTILLA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Organización de Estados Iberoamericanos (OEI)</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>https://www.educa.jcyl.es/profesorado/en/internacionalizacion-educacion-escolar/cooperacion-portugal</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Además, la Dirección General de Innovación y Formación del Profesorado trabaja con la Organización de Estados Iberoamericanos (OEI) en la puesta en marca de actuaciones de innovación educativa en cooperación con las autoridades lusas.</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
@@ -22680,7 +23186,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22692,7 +23197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -22721,7 +23226,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>International partners (2) - those with no country stated are last</t>
+          <t>International partners (10) - those with no country stated are last</t>
         </is>
       </c>
     </row>
@@ -22765,7 +23270,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DREVOREZ – Gabriel Vígh</t>
+          <t>MŠVVaŠ SR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -22780,7 +23285,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -22802,7 +23307,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Píla Svodín</t>
+          <t>KŠÚ v Nitre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -22817,7 +23322,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -22836,68 +23341,143 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ASŠaŠZS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Campuses (2)</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SAMP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Campus</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Verified?</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VŠLG Přerov</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Súkromná obchodná akadémia</t>
+          <t>VBC NITRA, s. r. o.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Štúrovo</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -22905,38 +23485,259 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>http://www.1soa-sturovo.sk/web/?page_id=32</t>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Elokované pracovisko SSŠ</t>
+          <t>TURR Baja</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>junior achievement sr</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DREVOREZ – Gabriel Vígh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Píla Svodín</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Campuses (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Verified?</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Súkromná obchodná akadémia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Štúrovo</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>http://www.1soa-sturovo.sk/web/?page_id=32</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Elokované pracovisko SSŠ – o. z. Súkromná obchodná akadémia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Nitra</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>http://www.1soa-sturovo.sk/web/?page_id=32</t>
         </is>
@@ -22947,8 +23748,16 @@
     <hyperlink ref="A2" location="'Institutions'!A2" display="← Back to all institutes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_hei/batch-20261003-2347/results.xlsx
+++ b/data_hei/batch-20261003-2347/results.xlsx
@@ -3801,17 +3801,29 @@
           <t>UNIVERSITE GRENOBLE ALPES</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Samuel Vergès</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Inserm Research Director</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3819,7 +3831,7 @@
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>https://www.univ-grenoble-alpes.fr/</t>
+          <t>https://www.univ-grenoble-alpes.fr/l-equipe-scientifique-de-l-expedition-5300-etudie-pour-la-premiere-fois-la-sante-des-femmes-soumises-a-des-conditions-d-altitude-extremes-1831977.kjsp?RH=1767714450161</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3881,17 +3893,29 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
+      <c r="AD29" s="1" t="inlineStr">
+        <is>
+          <t>https://www.univ-grenoble-alpes.fr/l-equipe-scientifique-de-l-expedition-5300-etudie-pour-la-premiere-fois-la-sante-des-femmes-soumises-a-des-conditions-d-altitude-extremes-1831977.kjsp?RH=1767714450161</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>L’équipe scientifique d’Expédition 5300, menée par Samuel Vergès, directeur de recherche Inserm au sein du Laboratoire hypoxie et physiopathologies cardiovasculaires et respiratoires (HP2 - UGA/CHUGA/Inserm) et soutenue par la Fondation UGA, est de retour au Pérou. Cette nouvelle mission est entièrement consacrée à l'adaptation physiologique des femmes vivants dans la ville la plus haute du monde, La Rinconada.</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>no contact found</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr"/>
+          <t>name found on page</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Other role. Samuel Vergès is an Inserm research director leading scientific expeditions and research teams at the institution.</t>
+        </is>
+      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>country;contact_name</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -3923,12 +3947,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>site found via: remembered from an earlier run. mode: gemini. 3 page(s) could not be read.</t>
+          <t>site found via: remembered from an earlier run. mode: gemini. 4 page(s) could not be read.</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:16Z</t>
+          <t>2026-10-22T20:35:29Z</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -3977,10 +4001,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId17"/>
     <hyperlink ref="M28" location="'r032 GROUPE EAC - ING'!A1" display="17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD28" r:id="rId18"/>
+    <hyperlink ref="B29" location="'Contacts'!A11" display="Samuel Vergès"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId19"/>
     <hyperlink ref="M29" location="'r033 UNIVERSITE GRENOBLE ALPES'!A1" display="2"/>
     <hyperlink ref="N29" location="'r033 UNIVERSITE GRENOBLE ALPES'!A1" display="2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD29" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16924,7 +16950,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:16Z</t>
+          <t>2026-10-22T20:35:29Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +17013,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:16Z</t>
+          <t>2026-10-22T20:35:29Z</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17825,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:16Z</t>
+          <t>2026-10-22T20:35:29Z</t>
         </is>
       </c>
     </row>
@@ -17856,7 +17882,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:16Z</t>
+          <t>2026-10-22T20:35:29Z</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18475,6 +18501,61 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>r033</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UNIVERSITE GRENOBLE ALPES</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Samuel Vergès</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Inserm Research Director</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>https://www.univ-grenoble-alpes.fr/l-equipe-scientifique-de-l-expedition-5300-etudie-pour-la-premiere-fois-la-sante-des-femmes-soumises-a-des-conditions-d-altitude-extremes-1831977.kjsp?RH=1767714450161</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L’équipe scientifique d’Expédition 5300, menée par Samuel Vergès, directeur de recherche Inserm au sein du Laboratoire hypoxie et physiopathologies cardiovasculaires et respiratoires (HP2 - UGA/CHUGA/Inserm) et soutenue par la Fondation UGA, est de retour au Pérou. Cette nouvelle mission est entièrement consacrée à l'adaptation physiologique des femmes vivants dans la ville la plus haute du monde, La Rinconada.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Other role. Samuel Vergès is an Inserm research director leading scientific expeditions and research teams at the institution.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>name found on page</t>
         </is>
       </c>
     </row>
@@ -18489,6 +18570,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
